--- a/Assets/Resources/MasterData/CardData.xlsx
+++ b/Assets/Resources/MasterData/CardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REBIRTH_GENESIS\3DTest\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE6C7F3-2526-4FCF-855D-E360753A708E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387F1344-D7BF-45FD-BC68-F478B29295E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8D1AA26D-1EB1-44B6-9ABB-10521DDCFE30}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="91">
   <si>
     <t>themeID</t>
     <phoneticPr fontId="2"/>
@@ -201,13 +201,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>カード名</t>
-    <rPh sb="3" eb="4">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>テーマ</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -221,13 +214,6 @@
   </si>
   <si>
     <t>SIZE</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>効果</t>
-    <rPh sb="0" eb="2">
-      <t>コウカ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -408,6 +394,26 @@
   </si>
   <si>
     <t>KoyakuID</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>size</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>atk</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>hp</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ability</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -888,7 +894,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>31</v>
@@ -897,28 +903,28 @@
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="I1" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>48</v>
+      <c r="J1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
@@ -944,7 +950,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H2" s="3">
         <f>_xlfn.XLOOKUP(G2,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
@@ -991,7 +997,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H3" s="3">
         <f>_xlfn.XLOOKUP(G3,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
@@ -1039,7 +1045,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H4" s="3">
         <f>_xlfn.XLOOKUP(G4,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
@@ -1088,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H5" s="3">
         <f>_xlfn.XLOOKUP(G5,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
@@ -1137,7 +1143,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H6" s="3">
         <f>_xlfn.XLOOKUP(G6,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
@@ -1186,7 +1192,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H7" s="3">
         <f>_xlfn.XLOOKUP(G7,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
@@ -1235,7 +1241,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H8" s="3">
         <f>_xlfn.XLOOKUP(G8,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
@@ -1281,7 +1287,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H9" s="3">
         <f>_xlfn.XLOOKUP(G9,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
@@ -1328,7 +1334,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H10" s="3">
         <f>_xlfn.XLOOKUP(G10,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
@@ -1374,7 +1380,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H11" s="3">
         <f>_xlfn.XLOOKUP(G11,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
@@ -1420,7 +1426,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H12" s="3">
         <f>_xlfn.XLOOKUP(G12,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
@@ -1469,7 +1475,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H13" s="3">
         <f>_xlfn.XLOOKUP(G13,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
@@ -2520,7 +2526,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="37.5" x14ac:dyDescent="0.4">
@@ -2529,7 +2535,7 @@
         <v>101</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="56.25" x14ac:dyDescent="0.4">
@@ -2538,7 +2544,7 @@
         <v>102</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="75" x14ac:dyDescent="0.4">
@@ -2547,7 +2553,7 @@
         <v>103</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.4">
@@ -2556,7 +2562,7 @@
         <v>104</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.4">
@@ -2565,7 +2571,7 @@
         <v>105</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="75" x14ac:dyDescent="0.4">
@@ -2574,7 +2580,7 @@
         <v>106</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
@@ -2583,7 +2589,7 @@
         <v>107</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="37.5" x14ac:dyDescent="0.4">
@@ -2592,7 +2598,7 @@
         <v>108</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
@@ -2601,7 +2607,7 @@
         <v>109</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
@@ -2610,7 +2616,7 @@
         <v>110</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="75" x14ac:dyDescent="0.4">
@@ -2619,7 +2625,7 @@
         <v>111</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="75" x14ac:dyDescent="0.4">
@@ -2628,7 +2634,7 @@
         <v>112</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="37.5" x14ac:dyDescent="0.4">
@@ -2637,7 +2643,7 @@
         <v>113</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="37.5" x14ac:dyDescent="0.4">
@@ -2646,7 +2652,7 @@
         <v>114</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
@@ -2655,7 +2661,7 @@
         <v>115</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
@@ -2664,7 +2670,7 @@
         <v>116</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
@@ -2673,7 +2679,7 @@
         <v>117</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
@@ -2682,7 +2688,7 @@
         <v>118</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
@@ -2691,7 +2697,7 @@
         <v>119</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
@@ -2700,7 +2706,7 @@
         <v>120</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
@@ -2709,7 +2715,7 @@
         <v>121</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
@@ -2718,7 +2724,7 @@
         <v>122</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -2737,13 +2743,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
@@ -3096,7 +3102,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
@@ -3104,7 +3110,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
@@ -3112,7 +3118,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
@@ -3120,7 +3126,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
@@ -3128,7 +3134,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
@@ -3136,7 +3142,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
@@ -3144,7 +3150,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
@@ -3160,7 +3166,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/MasterData/CardData.xlsx
+++ b/Assets/Resources/MasterData/CardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REBIRTH_GENESIS\3DTest\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387F1344-D7BF-45FD-BC68-F478B29295E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275BE123-CB99-439F-9D04-3D7DEC96F020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8D1AA26D-1EB1-44B6-9ABB-10521DDCFE30}"/>
   </bookViews>
@@ -987,7 +987,7 @@
       </c>
       <c r="D3" s="3">
         <f>_xlfn.XLOOKUP(C3,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>40</v>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="D4" s="3">
         <f>_xlfn.XLOOKUP(C4,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>40</v>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="D6" s="3">
         <f>_xlfn.XLOOKUP(C6,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>40</v>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="D7" s="3">
         <f>_xlfn.XLOOKUP(C7,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>40</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D12" s="3">
         <f>_xlfn.XLOOKUP(C12,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>40</v>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="D13" s="3">
         <f>_xlfn.XLOOKUP(C13,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>40</v>
@@ -2448,7 +2448,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>37</v>
@@ -2457,6 +2457,7 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Assets/Resources/MasterData/CardData.xlsx
+++ b/Assets/Resources/MasterData/CardData.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REBIRTH_GENESIS\3DTest\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275BE123-CB99-439F-9D04-3D7DEC96F020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B641B8C-C4CA-45A5-AB22-0457E9601A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8D1AA26D-1EB1-44B6-9ABB-10521DDCFE30}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{8D1AA26D-1EB1-44B6-9ABB-10521DDCFE30}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Name" sheetId="4" r:id="rId2"/>
-    <sheet name="Rarity" sheetId="5" r:id="rId3"/>
-    <sheet name="Theme" sheetId="6" r:id="rId4"/>
-    <sheet name="Ability" sheetId="3" r:id="rId5"/>
-    <sheet name="Status" sheetId="2" r:id="rId6"/>
-    <sheet name="Koyaku" sheetId="7" r:id="rId7"/>
+    <sheet name="Type" sheetId="8" r:id="rId2"/>
+    <sheet name="Name" sheetId="4" r:id="rId3"/>
+    <sheet name="Rarity" sheetId="5" r:id="rId4"/>
+    <sheet name="Theme" sheetId="6" r:id="rId5"/>
+    <sheet name="Ability" sheetId="3" r:id="rId6"/>
+    <sheet name="Status" sheetId="2" r:id="rId7"/>
+    <sheet name="Koyaku" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="97">
   <si>
     <t>themeID</t>
     <phoneticPr fontId="2"/>
@@ -414,6 +415,28 @@
   </si>
   <si>
     <t>ability</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>カードタイプ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>モンスター</t>
+  </si>
+  <si>
+    <t>モンスター</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スペル</t>
+  </si>
+  <si>
+    <t>スペル</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -445,7 +468,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -488,6 +511,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -518,7 +553,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -556,6 +591,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -878,7 +919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D7DF1B-AB83-4006-8569-97B2E1F4F177}">
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="16.625" bestFit="1" customWidth="1"/>
@@ -886,10 +927,12 @@
     <col min="6" max="6" width="9" customWidth="1"/>
     <col min="7" max="7" width="16.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="12" max="12" width="205.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="205.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -923,11 +966,17 @@
       <c r="K1" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" s="3">
         <v>101</v>
       </c>
@@ -968,13 +1017,20 @@
         <f>_xlfn.XLOOKUP(A2,Status!A:A,Status!D:D,"")</f>
         <v>11</v>
       </c>
-      <c r="L2" s="3" t="str">
+      <c r="L2" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M2" s="3">
+        <f>_xlfn.XLOOKUP(L2,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>0</v>
+      </c>
+      <c r="N2" s="3" t="str">
         <f>_xlfn.XLOOKUP(A2,Ability!A:A,Ability!B:B,"")</f>
         <v>①召喚時、手札を1枚捨ててもよい。そうしたら山札の上から5枚見て、種族に「ロボ」を含むカードを１枚手札に加える。
 ②レベルアップ</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
         <v>102</v>
       </c>
@@ -1015,14 +1071,21 @@
         <f>_xlfn.XLOOKUP(A3,Status!A:A,Status!D:D,"")</f>
         <v>14</v>
       </c>
-      <c r="L3" s="3" t="str">
+      <c r="L3" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M3" s="3">
+        <f>_xlfn.XLOOKUP(L3,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="3" t="str">
         <f>_xlfn.XLOOKUP(A3,Ability!A:A,Ability!B:B,"")</f>
         <v>①ターン終了時プレイヤーのHPを2回復する。
 ②このモンスターが攻撃を受けた時このモンスターのHPを1回復する。
 ③レベルアップ</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>103</v>
       </c>
@@ -1063,7 +1126,14 @@
         <f>_xlfn.XLOOKUP(A4,Status!A:A,Status!D:D,"")</f>
         <v>17</v>
       </c>
-      <c r="L4" s="3" t="str">
+      <c r="L4" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M4" s="3">
+        <f>_xlfn.XLOOKUP(L4,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="3" t="str">
         <f>_xlfn.XLOOKUP(A4,Ability!A:A,Ability!B:B,"")</f>
         <v>①このモンスターが攻撃を受けた時このモンスターのatkを1上昇する。
 ②このモンスターの対応役成立時、自分フィールドのモンスター全てと自分のHPを1回復する。
@@ -1071,7 +1141,7 @@
 ④アスリート</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>104</v>
       </c>
@@ -1112,7 +1182,14 @@
         <f>_xlfn.XLOOKUP(A5,Status!A:A,Status!D:D,"")</f>
         <v>10</v>
       </c>
-      <c r="L5" s="3" t="str">
+      <c r="L5" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M5" s="3">
+        <f>_xlfn.XLOOKUP(L5,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" t="str">
         <f>_xlfn.XLOOKUP(A5,Ability!A:A,Ability!B:B,"")</f>
         <v>①召喚時、相手プレイヤーか相手モンスター1体に2ダメージ。
 ②ターン終了時、山札の上から3枚を見てスペルを1枚手札に加える。
@@ -1120,7 +1197,7 @@
 ④レベルアップ</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
         <v>105</v>
       </c>
@@ -1161,7 +1238,14 @@
         <f>_xlfn.XLOOKUP(A6,Status!A:A,Status!D:D,"")</f>
         <v>12</v>
       </c>
-      <c r="L6" s="3" t="str">
+      <c r="L6" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M6" s="3">
+        <f>_xlfn.XLOOKUP(L6,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="str">
         <f>_xlfn.XLOOKUP(A6,Ability!A:A,Ability!B:B,"")</f>
         <v>①ターン開始時、相手のすべてのモンスターに1ダメージ与える。
 ②ターン終了時、相手のランダムなモンスターに3ダメージ与える。
@@ -1169,7 +1253,7 @@
 ④レベルアップ</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <v>106</v>
       </c>
@@ -1210,7 +1294,14 @@
         <f>_xlfn.XLOOKUP(A7,Status!A:A,Status!D:D,"")</f>
         <v>15</v>
       </c>
-      <c r="L7" s="3" t="str">
+      <c r="L7" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M7" s="3">
+        <f>_xlfn.XLOOKUP(L7,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="str">
         <f>_xlfn.XLOOKUP(A7,Ability!A:A,Ability!B:B,"")</f>
         <v>①ターン開始時、自分のモンスターを1体選ぶ。このターンそのモンスターのatkを+3する。
 ②対応役成立時、カードを1枚引く。
@@ -1218,7 +1309,7 @@
 ④アスリート</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" s="3">
         <v>107</v>
       </c>
@@ -1259,12 +1350,19 @@
         <f>_xlfn.XLOOKUP(A8,Status!A:A,Status!D:D,"")</f>
         <v>4</v>
       </c>
-      <c r="L8" s="3" t="str">
+      <c r="L8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M8" s="3">
+        <f>_xlfn.XLOOKUP(L8,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" t="str">
         <f>_xlfn.XLOOKUP(A8,Ability!A:A,Ability!B:B,"")</f>
         <v>①ターゲット集中</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9" s="3">
         <v>108</v>
       </c>
@@ -1305,13 +1403,20 @@
         <f>_xlfn.XLOOKUP(A9,Status!A:A,Status!D:D,"")</f>
         <v>10</v>
       </c>
-      <c r="L9" s="3" t="str">
+      <c r="L9" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M9" s="3">
+        <f>_xlfn.XLOOKUP(L9,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="3" t="str">
         <f>_xlfn.XLOOKUP(A9,Ability!A:A,Ability!B:B,"")</f>
         <v>①召喚時ランダムな敵に2ダメージ
 ②アスリート</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10" s="3">
         <v>109</v>
       </c>
@@ -1352,12 +1457,19 @@
         <f>_xlfn.XLOOKUP(A10,Status!A:A,Status!D:D,"")</f>
         <v>10</v>
       </c>
-      <c r="L10" s="3" t="str">
+      <c r="L10" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M10" s="3">
+        <f>_xlfn.XLOOKUP(L10,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="3" t="str">
         <f>_xlfn.XLOOKUP(A10,Ability!A:A,Ability!B:B,"")</f>
         <v>①ターン終了時、カードを1枚引く。</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11" s="3">
         <v>110</v>
       </c>
@@ -1398,12 +1510,19 @@
         <f>_xlfn.XLOOKUP(A11,Status!A:A,Status!D:D,"")</f>
         <v>8</v>
       </c>
-      <c r="L11" s="3" t="str">
+      <c r="L11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M11" s="3">
+        <f>_xlfn.XLOOKUP(L11,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="3" t="str">
         <f>_xlfn.XLOOKUP(A11,Ability!A:A,Ability!B:B,"")</f>
         <v>①召喚時デッキの上から3枚を見て、その中から「ロボ」モンスターを全て手札に加える。(この効果は各ターン1度しか発動しない。)</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12" s="3">
         <v>111</v>
       </c>
@@ -1444,7 +1563,14 @@
         <f>_xlfn.XLOOKUP(A12,Status!A:A,Status!D:D,"")</f>
         <v>30</v>
       </c>
-      <c r="L12" s="3" t="str">
+      <c r="L12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M12" s="3">
+        <f>_xlfn.XLOOKUP(L12,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="3" t="str">
         <f>_xlfn.XLOOKUP(A12,Ability!A:A,Ability!B:B,"")</f>
         <v>①召喚時、自分のモンスターのHPを全回復する。
 ②対応役成立時、このターンこのモンスターのatkを+5する。
@@ -1452,7 +1578,7 @@
 ④アスリート</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13" s="3">
         <v>112</v>
       </c>
@@ -1493,7 +1619,14 @@
         <f>_xlfn.XLOOKUP(A13,Status!A:A,Status!D:D,"")</f>
         <v>0</v>
       </c>
-      <c r="L13" s="3" t="str">
+      <c r="L13" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M13" s="3">
+        <f>_xlfn.XLOOKUP(L13,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="3" t="str">
         <f>_xlfn.XLOOKUP(A13,Ability!A:A,Ability!B:B,"")</f>
         <v>①相手のターン中このモンスターのatkは∞になる。
 ②このモンスターは離れない。
@@ -1501,7 +1634,7 @@
 ④反撃</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A14" s="3">
         <v>113</v>
       </c>
@@ -1542,13 +1675,20 @@
         <f>_xlfn.XLOOKUP(A14,Status!A:A,Status!D:D,"")</f>
         <v>-1</v>
       </c>
-      <c r="L14" s="3" t="str">
+      <c r="L14" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="M14" s="3">
+        <f>_xlfn.XLOOKUP(L14,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>1</v>
+      </c>
+      <c r="N14" s="3" t="str">
         <f>_xlfn.XLOOKUP(A14,Ability!A:A,Ability!B:B,"")</f>
         <v>このターンテーブルを1上昇。(この効果は各ターンに1度しか使えない)
 レベルアップ効果を持つ「RG」モンスターをレベルアップ。</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15" s="3">
         <v>114</v>
       </c>
@@ -1589,13 +1729,20 @@
         <f>_xlfn.XLOOKUP(A15,Status!A:A,Status!D:D,"")</f>
         <v>-1</v>
       </c>
-      <c r="L15" s="3" t="str">
+      <c r="L15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="M15" s="3">
+        <f>_xlfn.XLOOKUP(L15,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>1</v>
+      </c>
+      <c r="N15" s="3" t="str">
         <f>_xlfn.XLOOKUP(A15,Ability!A:A,Ability!B:B,"")</f>
         <v>相手のモンスターを1体選ぶ。そのモンスターは次の相手のターンに攻撃できない。
 レベルアップ効果を持つ「RG」１体のモンスターをレベルアップ。</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A16" s="3">
         <v>115</v>
       </c>
@@ -1636,12 +1783,19 @@
         <f>_xlfn.XLOOKUP(A16,Status!A:A,Status!D:D,"")</f>
         <v>-1</v>
       </c>
-      <c r="L16" s="3" t="str">
+      <c r="L16" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="M16" s="3">
+        <f>_xlfn.XLOOKUP(L16,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>1</v>
+      </c>
+      <c r="N16" s="3" t="str">
         <f>_xlfn.XLOOKUP(A16,Ability!A:A,Ability!B:B,"")</f>
         <v>次の自分のターンまでモンスター1体に「ターゲット集中」を与える。</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A17" s="3">
         <v>116</v>
       </c>
@@ -1682,12 +1836,19 @@
         <f>_xlfn.XLOOKUP(A17,Status!A:A,Status!D:D,"")</f>
         <v>-1</v>
       </c>
-      <c r="L17" s="3" t="str">
+      <c r="L17" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="M17" s="3">
+        <f>_xlfn.XLOOKUP(L17,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>1</v>
+      </c>
+      <c r="N17" s="3" t="str">
         <f>_xlfn.XLOOKUP(A17,Ability!A:A,Ability!B:B,"")</f>
         <v>自分のサイズ2以下のモンスターを1体選ぶ。次の自分のターンまでそのモンスターは対応役成立につき2回攻撃する。</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A18" s="3">
         <v>117</v>
       </c>
@@ -1728,12 +1889,19 @@
         <f>_xlfn.XLOOKUP(A18,Status!A:A,Status!D:D,"")</f>
         <v>-1</v>
       </c>
-      <c r="L18" s="3" t="str">
+      <c r="L18" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="M18" s="3">
+        <f>_xlfn.XLOOKUP(L18,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>1</v>
+      </c>
+      <c r="N18" s="3" t="str">
         <f>_xlfn.XLOOKUP(A18,Ability!A:A,Ability!B:B,"")</f>
         <v>山札の上から7枚見て「ロボ」を種族に含むモンスターを手札に加える。(この効果は各ターンに1度しか使えない)</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A19" s="3">
         <v>118</v>
       </c>
@@ -1774,12 +1942,19 @@
         <f>_xlfn.XLOOKUP(A19,Status!A:A,Status!D:D,"")</f>
         <v>-1</v>
       </c>
-      <c r="L19" s="3" t="str">
+      <c r="L19" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="M19" s="3">
+        <f>_xlfn.XLOOKUP(L19,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>1</v>
+      </c>
+      <c r="N19" s="3" t="str">
         <f>_xlfn.XLOOKUP(A19,Ability!A:A,Ability!B:B,"")</f>
         <v>「RG」を名称に含むモンスターのレベルを上げる。</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A20" s="3">
         <v>119</v>
       </c>
@@ -1820,12 +1995,19 @@
         <f>_xlfn.XLOOKUP(A20,Status!A:A,Status!D:D,"")</f>
         <v>-1</v>
       </c>
-      <c r="L20" s="3" t="str">
+      <c r="L20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="M20" s="3">
+        <f>_xlfn.XLOOKUP(L20,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>1</v>
+      </c>
+      <c r="N20" s="3" t="str">
         <f>_xlfn.XLOOKUP(A20,Ability!A:A,Ability!B:B,"")</f>
         <v>自分のモンスターを1体選ぶ。そのモンスターは次の自分のターンまで、受けるダメージを-2する。</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A21" s="3">
         <v>120</v>
       </c>
@@ -1866,12 +2048,19 @@
         <f>_xlfn.XLOOKUP(A21,Status!A:A,Status!D:D,"")</f>
         <v>-1</v>
       </c>
-      <c r="L21" s="3" t="str">
+      <c r="L21" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="M21" s="3">
+        <f>_xlfn.XLOOKUP(L21,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>1</v>
+      </c>
+      <c r="N21" s="3" t="str">
         <f>_xlfn.XLOOKUP(A21,Ability!A:A,Ability!B:B,"")</f>
         <v>墓地からatk4以下のモンスターを出す</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A22" s="3">
         <v>121</v>
       </c>
@@ -1912,12 +2101,19 @@
         <f>_xlfn.XLOOKUP(A22,Status!A:A,Status!D:D,"")</f>
         <v>-1</v>
       </c>
-      <c r="L22" s="3" t="str">
+      <c r="L22" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="M22" s="3">
+        <f>_xlfn.XLOOKUP(L22,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>1</v>
+      </c>
+      <c r="N22" s="3" t="str">
         <f>_xlfn.XLOOKUP(A22,Ability!A:A,Ability!B:B,"")</f>
         <v>カードを2枚引く。(この効果は各ターンに1度しか使えない)</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A23" s="3">
         <v>122</v>
       </c>
@@ -1958,12 +2154,19 @@
         <f>_xlfn.XLOOKUP(A23,Status!A:A,Status!D:D,"")</f>
         <v>-1</v>
       </c>
-      <c r="L23" s="3" t="str">
+      <c r="L23" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="M23" s="3">
+        <f>_xlfn.XLOOKUP(L23,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>1</v>
+      </c>
+      <c r="N23" s="3" t="str">
         <f>_xlfn.XLOOKUP(A23,Ability!A:A,Ability!B:B,"")</f>
         <v>相手のすべてのモンスターに2ダメージを与える</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A24" s="3">
         <v>201</v>
       </c>
@@ -1981,8 +2184,10 @@
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A25" s="3">
         <v>202</v>
       </c>
@@ -2000,8 +2205,10 @@
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A26" s="3">
         <v>203</v>
       </c>
@@ -2019,8 +2226,10 @@
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A27" s="3">
         <v>204</v>
       </c>
@@ -2038,8 +2247,10 @@
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A28" s="3">
         <v>205</v>
       </c>
@@ -2057,8 +2268,10 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A29" s="3">
         <v>206</v>
       </c>
@@ -2076,8 +2289,10 @@
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A30" s="3">
         <v>207</v>
       </c>
@@ -2095,6 +2310,8 @@
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -2107,7 +2324,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FB6E8B83-655D-43E5-9D49-125D76F5837E}">
           <x14:formula1>
             <xm:f>Rarity!$B$2:$B$6</xm:f>
@@ -2126,6 +2343,12 @@
           </x14:formula1>
           <xm:sqref>G2:G23</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6E6FA480-3F73-49E6-A9B4-9ABB5FEEA2C3}">
+          <x14:formula1>
+            <xm:f>Type!$B$2:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>L2:L23</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -2133,6 +2356,44 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A33A8186-81E6-4999-98A8-473762CE4656}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" s="3">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E8A908C-08CC-4BD3-930A-217BE796C531}">
   <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -2401,7 +2662,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B679988E-5CDF-4EB3-B228-46145FEE67AE}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -2461,7 +2722,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E31A59C-D3E7-45EE-AB0E-7351C0993DCD}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -2514,7 +2775,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C63B9C-DB74-4E28-B879-D59019679859}">
   <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -2734,7 +2995,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E0DEF2-88A1-42B6-9AE3-11FF6185453D}">
   <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -3090,7 +3351,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A11AEFB-2CB3-4B10-99EE-D988C439CE1A}">
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>

--- a/Assets/Resources/MasterData/CardData.xlsx
+++ b/Assets/Resources/MasterData/CardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REBIRTH_GENESIS\3DTest\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B641B8C-C4CA-45A5-AB22-0457E9601A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E01DBD7-6DA2-4137-8E23-760714A45DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{8D1AA26D-1EB1-44B6-9ABB-10521DDCFE30}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8D1AA26D-1EB1-44B6-9ABB-10521DDCFE30}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="94">
   <si>
     <t>themeID</t>
     <phoneticPr fontId="2"/>
@@ -394,26 +394,10 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>KoyakuID</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>name</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>size</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>atk</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>hp</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ability</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -437,6 +421,10 @@
   </si>
   <si>
     <t>スペル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>suportRoleID</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -926,7 +914,7 @@
     <col min="3" max="5" width="16.625" customWidth="1"/>
     <col min="6" max="6" width="9" customWidth="1"/>
     <col min="7" max="7" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12.875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5.625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="205.75" bestFit="1" customWidth="1"/>
@@ -937,7 +925,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>31</v>
@@ -955,25 +943,25 @@
         <v>84</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="N1" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.4">
@@ -1018,7 +1006,7 @@
         <v>11</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M2" s="3">
         <f>_xlfn.XLOOKUP(L2,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1072,7 +1060,7 @@
         <v>14</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M3" s="3">
         <f>_xlfn.XLOOKUP(L3,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1127,7 +1115,7 @@
         <v>17</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M4" s="3">
         <f>_xlfn.XLOOKUP(L4,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1183,7 +1171,7 @@
         <v>10</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M5" s="3">
         <f>_xlfn.XLOOKUP(L5,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1239,7 +1227,7 @@
         <v>12</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M6" s="3">
         <f>_xlfn.XLOOKUP(L6,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1295,7 +1283,7 @@
         <v>15</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M7" s="3">
         <f>_xlfn.XLOOKUP(L7,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1351,7 +1339,7 @@
         <v>4</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M8" s="3">
         <f>_xlfn.XLOOKUP(L8,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1404,7 +1392,7 @@
         <v>10</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M9" s="3">
         <f>_xlfn.XLOOKUP(L9,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1458,7 +1446,7 @@
         <v>10</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M10" s="3">
         <f>_xlfn.XLOOKUP(L10,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1511,7 +1499,7 @@
         <v>8</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M11" s="3">
         <f>_xlfn.XLOOKUP(L11,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1564,7 +1552,7 @@
         <v>30</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M12" s="3">
         <f>_xlfn.XLOOKUP(L12,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1620,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M13" s="3">
         <f>_xlfn.XLOOKUP(L13,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1676,7 +1664,7 @@
         <v>-1</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M14" s="3">
         <f>_xlfn.XLOOKUP(L14,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1730,7 +1718,7 @@
         <v>-1</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M15" s="3">
         <f>_xlfn.XLOOKUP(L15,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1784,7 +1772,7 @@
         <v>-1</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M16" s="3">
         <f>_xlfn.XLOOKUP(L16,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1837,7 +1825,7 @@
         <v>-1</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M17" s="3">
         <f>_xlfn.XLOOKUP(L17,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1890,7 +1878,7 @@
         <v>-1</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M18" s="3">
         <f>_xlfn.XLOOKUP(L18,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1943,7 +1931,7 @@
         <v>-1</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M19" s="3">
         <f>_xlfn.XLOOKUP(L19,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1996,7 +1984,7 @@
         <v>-1</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M20" s="3">
         <f>_xlfn.XLOOKUP(L20,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2049,7 +2037,7 @@
         <v>-1</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M21" s="3">
         <f>_xlfn.XLOOKUP(L21,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2102,7 +2090,7 @@
         <v>-1</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M22" s="3">
         <f>_xlfn.XLOOKUP(L22,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2155,7 +2143,7 @@
         <v>-1</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M23" s="3">
         <f>_xlfn.XLOOKUP(L23,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2368,7 +2356,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
@@ -2376,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
@@ -2384,7 +2372,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/MasterData/CardData.xlsx
+++ b/Assets/Resources/MasterData/CardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REBIRTH_GENESIS\3DTest\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E01DBD7-6DA2-4137-8E23-760714A45DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9646C642-DC9C-4DF8-863B-B2CE45AB3A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8D1AA26D-1EB1-44B6-9ABB-10521DDCFE30}"/>
   </bookViews>
@@ -990,7 +990,7 @@
         <v>71</v>
       </c>
       <c r="H2" s="3">
-        <f>_xlfn.XLOOKUP(G2,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
+        <f>_xlfn.XLOOKUP(G2,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>5</v>
       </c>
       <c r="I2" s="3">
@@ -1044,7 +1044,7 @@
         <v>71</v>
       </c>
       <c r="H3" s="3">
-        <f>_xlfn.XLOOKUP(G3,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
+        <f>_xlfn.XLOOKUP(G3,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>5</v>
       </c>
       <c r="I3" s="3">
@@ -1099,7 +1099,7 @@
         <v>71</v>
       </c>
       <c r="H4" s="3">
-        <f>_xlfn.XLOOKUP(G4,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
+        <f>_xlfn.XLOOKUP(G4,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>5</v>
       </c>
       <c r="I4" s="3">
@@ -1155,7 +1155,7 @@
         <v>73</v>
       </c>
       <c r="H5" s="3">
-        <f>_xlfn.XLOOKUP(G5,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
+        <f>_xlfn.XLOOKUP(G5,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>3</v>
       </c>
       <c r="I5" s="3">
@@ -1211,7 +1211,7 @@
         <v>73</v>
       </c>
       <c r="H6" s="3">
-        <f>_xlfn.XLOOKUP(G6,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
+        <f>_xlfn.XLOOKUP(G6,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>3</v>
       </c>
       <c r="I6" s="3">
@@ -1267,7 +1267,7 @@
         <v>73</v>
       </c>
       <c r="H7" s="3">
-        <f>_xlfn.XLOOKUP(G7,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
+        <f>_xlfn.XLOOKUP(G7,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>3</v>
       </c>
       <c r="I7" s="3">
@@ -1323,7 +1323,7 @@
         <v>79</v>
       </c>
       <c r="H8" s="3">
-        <f>_xlfn.XLOOKUP(G8,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
+        <f>_xlfn.XLOOKUP(G8,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>4</v>
       </c>
       <c r="I8" s="3">
@@ -1376,7 +1376,7 @@
         <v>77</v>
       </c>
       <c r="H9" s="3">
-        <f>_xlfn.XLOOKUP(G9,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
+        <f>_xlfn.XLOOKUP(G9,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>2</v>
       </c>
       <c r="I9" s="3">
@@ -1430,7 +1430,7 @@
         <v>75</v>
       </c>
       <c r="H10" s="3">
-        <f>_xlfn.XLOOKUP(G10,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
+        <f>_xlfn.XLOOKUP(G10,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>1</v>
       </c>
       <c r="I10" s="3">
@@ -1483,7 +1483,7 @@
         <v>75</v>
       </c>
       <c r="H11" s="3">
-        <f>_xlfn.XLOOKUP(G11,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
+        <f>_xlfn.XLOOKUP(G11,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>1</v>
       </c>
       <c r="I11" s="3">
@@ -1536,8 +1536,8 @@
         <v>82</v>
       </c>
       <c r="H12" s="3">
-        <f>_xlfn.XLOOKUP(G12,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
-        <v>8</v>
+        <f>_xlfn.XLOOKUP(G12,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
+        <v>7</v>
       </c>
       <c r="I12" s="3">
         <f>_xlfn.XLOOKUP(A12,Status!A:A,Status!B:B,"")</f>
@@ -1592,7 +1592,7 @@
         <v>81</v>
       </c>
       <c r="H13" s="3">
-        <f>_xlfn.XLOOKUP(G13,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
+        <f>_xlfn.XLOOKUP(G13,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>6</v>
       </c>
       <c r="I13" s="3">
@@ -1648,8 +1648,8 @@
         <v>36</v>
       </c>
       <c r="H14" s="3">
-        <f>_xlfn.XLOOKUP(G14,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
-        <v>7</v>
+        <f>_xlfn.XLOOKUP(G14,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
+        <v>0</v>
       </c>
       <c r="I14" s="3">
         <f>_xlfn.XLOOKUP(A14,Status!A:A,Status!B:B,"")</f>
@@ -1702,8 +1702,8 @@
         <v>36</v>
       </c>
       <c r="H15" s="3">
-        <f>_xlfn.XLOOKUP(G15,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
-        <v>7</v>
+        <f>_xlfn.XLOOKUP(G15,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
         <f>_xlfn.XLOOKUP(A15,Status!A:A,Status!B:B,"")</f>
@@ -1756,8 +1756,8 @@
         <v>36</v>
       </c>
       <c r="H16" s="3">
-        <f>_xlfn.XLOOKUP(G16,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
-        <v>7</v>
+        <f>_xlfn.XLOOKUP(G16,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
+        <v>0</v>
       </c>
       <c r="I16" s="3">
         <f>_xlfn.XLOOKUP(A16,Status!A:A,Status!B:B,"")</f>
@@ -1809,8 +1809,8 @@
         <v>36</v>
       </c>
       <c r="H17" s="3">
-        <f>_xlfn.XLOOKUP(G17,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
-        <v>7</v>
+        <f>_xlfn.XLOOKUP(G17,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
+        <v>0</v>
       </c>
       <c r="I17" s="3">
         <f>_xlfn.XLOOKUP(A17,Status!A:A,Status!B:B,"")</f>
@@ -1862,8 +1862,8 @@
         <v>36</v>
       </c>
       <c r="H18" s="3">
-        <f>_xlfn.XLOOKUP(G18,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
-        <v>7</v>
+        <f>_xlfn.XLOOKUP(G18,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
+        <v>0</v>
       </c>
       <c r="I18" s="3">
         <f>_xlfn.XLOOKUP(A18,Status!A:A,Status!B:B,"")</f>
@@ -1915,8 +1915,8 @@
         <v>36</v>
       </c>
       <c r="H19" s="3">
-        <f>_xlfn.XLOOKUP(G19,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
-        <v>7</v>
+        <f>_xlfn.XLOOKUP(G19,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
+        <v>0</v>
       </c>
       <c r="I19" s="3">
         <f>_xlfn.XLOOKUP(A19,Status!A:A,Status!B:B,"")</f>
@@ -1968,8 +1968,8 @@
         <v>36</v>
       </c>
       <c r="H20" s="3">
-        <f>_xlfn.XLOOKUP(G20,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
-        <v>7</v>
+        <f>_xlfn.XLOOKUP(G20,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
         <f>_xlfn.XLOOKUP(A20,Status!A:A,Status!B:B,"")</f>
@@ -2021,8 +2021,8 @@
         <v>36</v>
       </c>
       <c r="H21" s="3">
-        <f>_xlfn.XLOOKUP(G21,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
-        <v>7</v>
+        <f>_xlfn.XLOOKUP(G21,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
         <f>_xlfn.XLOOKUP(A21,Status!A:A,Status!B:B,"")</f>
@@ -2074,8 +2074,8 @@
         <v>36</v>
       </c>
       <c r="H22" s="3">
-        <f>_xlfn.XLOOKUP(G22,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
-        <v>7</v>
+        <f>_xlfn.XLOOKUP(G22,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
+        <v>0</v>
       </c>
       <c r="I22" s="3">
         <f>_xlfn.XLOOKUP(A22,Status!A:A,Status!B:B,"")</f>
@@ -2127,8 +2127,8 @@
         <v>36</v>
       </c>
       <c r="H23" s="3">
-        <f>_xlfn.XLOOKUP(G23,Koyaku!$B$2:$B$20,Koyaku!$A$2:$A$20,"")</f>
-        <v>7</v>
+        <f>_xlfn.XLOOKUP(G23,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
+        <v>0</v>
       </c>
       <c r="I23" s="3">
         <f>_xlfn.XLOOKUP(A23,Status!A:A,Status!B:B,"")</f>
@@ -2312,7 +2312,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FB6E8B83-655D-43E5-9D49-125D76F5837E}">
           <x14:formula1>
             <xm:f>Rarity!$B$2:$B$6</xm:f>
@@ -2325,17 +2325,23 @@
           </x14:formula1>
           <xm:sqref>E2:E23</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1B3501F0-A3BC-49B7-9401-98C97ACDC1EF}">
-          <x14:formula1>
-            <xm:f>Koyaku!$B$2:$B$9</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2:G23</xm:sqref>
-        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6E6FA480-3F73-49E6-A9B4-9ABB5FEEA2C3}">
           <x14:formula1>
             <xm:f>Type!$B$2:$B$3</xm:f>
           </x14:formula1>
           <xm:sqref>L2:L23</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1B3501F0-A3BC-49B7-9401-98C97ACDC1EF}">
+          <x14:formula1>
+            <xm:f>Koyaku!$B$3:$B$9</xm:f>
+          </x14:formula1>
+          <xm:sqref>G3:G23</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4686C655-AE29-417D-8727-81DB9BE7AC31}">
+          <x14:formula1>
+            <xm:f>Koyaku!$B$2:$B$9</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3357,63 +3363,63 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>83</v>
@@ -3422,5 +3428,6 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Resources/MasterData/CardData.xlsx
+++ b/Assets/Resources/MasterData/CardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REBIRTH_GENESIS\3DTest\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9646C642-DC9C-4DF8-863B-B2CE45AB3A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F709B37-ACE1-49C9-B279-1EB9FAB27046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8D1AA26D-1EB1-44B6-9ABB-10521DDCFE30}"/>
   </bookViews>
@@ -20,7 +20,8 @@
     <sheet name="Theme" sheetId="6" r:id="rId5"/>
     <sheet name="Ability" sheetId="3" r:id="rId6"/>
     <sheet name="Status" sheetId="2" r:id="rId7"/>
-    <sheet name="Koyaku" sheetId="7" r:id="rId8"/>
+    <sheet name="Race" sheetId="9" r:id="rId8"/>
+    <sheet name="Koyaku" sheetId="7" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="105">
   <si>
     <t>themeID</t>
     <phoneticPr fontId="2"/>
@@ -425,6 +426,67 @@
   </si>
   <si>
     <t>suportRoleID</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>種族1</t>
+    <rPh sb="0" eb="2">
+      <t>シュゾク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>なし</t>
+  </si>
+  <si>
+    <t>なし</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>戦士</t>
+    <rPh sb="0" eb="2">
+      <t>センシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>人</t>
+    <rPh sb="0" eb="1">
+      <t>ヒト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>種族</t>
+    <rPh sb="0" eb="2">
+      <t>シュゾク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FirstRaceID</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>種族2</t>
+    <rPh sb="0" eb="2">
+      <t>シュゾク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SecondRaceID</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>種族3</t>
+    <rPh sb="0" eb="2">
+      <t>シュゾク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ThildRaceID</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -907,7 +969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D7DF1B-AB83-4006-8569-97B2E1F4F177}">
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:T30"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="16.625" bestFit="1" customWidth="1"/>
@@ -915,12 +977,15 @@
     <col min="6" max="6" width="9" customWidth="1"/>
     <col min="7" max="7" width="16.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="205.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="12.875" customWidth="1"/>
+    <col min="12" max="12" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.375" customWidth="1"/>
+    <col min="18" max="18" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="205.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -945,26 +1010,44 @@
       <c r="H1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="R1" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A2" s="3">
         <v>101</v>
       </c>
@@ -993,32 +1076,53 @@
         <f>_xlfn.XLOOKUP(G2,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>5</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" s="3">
+        <f>_xlfn.XLOOKUP(I2,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="L2" s="3">
+        <f>_xlfn.XLOOKUP(K2,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N2" s="3">
+        <f>_xlfn.XLOOKUP(M2,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O2" s="3">
         <f>_xlfn.XLOOKUP(A2,Status!A:A,Status!B:B,"")</f>
         <v>2</v>
       </c>
-      <c r="J2" s="3">
+      <c r="P2" s="3">
         <f>_xlfn.XLOOKUP(A2,Status!A:A,Status!C:C,"")</f>
         <v>4</v>
       </c>
-      <c r="K2" s="3">
+      <c r="Q2" s="3">
         <f>_xlfn.XLOOKUP(A2,Status!A:A,Status!D:D,"")</f>
         <v>11</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="M2" s="3">
-        <f>_xlfn.XLOOKUP(L2,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+      <c r="S2" s="3">
+        <f>_xlfn.XLOOKUP(R2,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
         <v>0</v>
       </c>
-      <c r="N2" s="3" t="str">
+      <c r="T2" s="3" t="str">
         <f>_xlfn.XLOOKUP(A2,Ability!A:A,Ability!B:B,"")</f>
         <v>①召喚時、手札を1枚捨ててもよい。そうしたら山札の上から5枚見て、種族に「ロボ」を含むカードを１枚手札に加える。
 ②レベルアップ</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
         <v>102</v>
       </c>
@@ -1047,33 +1151,54 @@
         <f>_xlfn.XLOOKUP(G3,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>5</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="3">
+        <f>_xlfn.XLOOKUP(I3,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="L3" s="3">
+        <f>_xlfn.XLOOKUP(K3,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N3" s="3">
+        <f>_xlfn.XLOOKUP(M3,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O3" s="3">
         <f>_xlfn.XLOOKUP(A3,Status!A:A,Status!B:B,"")</f>
         <v>2</v>
       </c>
-      <c r="J3" s="3">
+      <c r="P3" s="3">
         <f>_xlfn.XLOOKUP(A3,Status!A:A,Status!C:C,"")</f>
         <v>6</v>
       </c>
-      <c r="K3" s="3">
+      <c r="Q3" s="3">
         <f>_xlfn.XLOOKUP(A3,Status!A:A,Status!D:D,"")</f>
         <v>14</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="M3" s="3">
-        <f>_xlfn.XLOOKUP(L3,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+      <c r="S3" s="3">
+        <f>_xlfn.XLOOKUP(R3,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
         <v>0</v>
       </c>
-      <c r="N3" s="3" t="str">
+      <c r="T3" s="3" t="str">
         <f>_xlfn.XLOOKUP(A3,Ability!A:A,Ability!B:B,"")</f>
         <v>①ターン終了時プレイヤーのHPを2回復する。
 ②このモンスターが攻撃を受けた時このモンスターのHPを1回復する。
 ③レベルアップ</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>103</v>
       </c>
@@ -1102,26 +1227,47 @@
         <f>_xlfn.XLOOKUP(G4,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>5</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="3">
+        <f>_xlfn.XLOOKUP(I4,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="L4" s="3">
+        <f>_xlfn.XLOOKUP(K4,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N4" s="3">
+        <f>_xlfn.XLOOKUP(M4,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O4" s="3">
         <f>_xlfn.XLOOKUP(A4,Status!A:A,Status!B:B,"")</f>
         <v>2</v>
       </c>
-      <c r="J4" s="3">
+      <c r="P4" s="3">
         <f>_xlfn.XLOOKUP(A4,Status!A:A,Status!C:C,"")</f>
         <v>8</v>
       </c>
-      <c r="K4" s="3">
+      <c r="Q4" s="3">
         <f>_xlfn.XLOOKUP(A4,Status!A:A,Status!D:D,"")</f>
         <v>17</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="R4" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="M4" s="3">
-        <f>_xlfn.XLOOKUP(L4,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+      <c r="S4" s="3">
+        <f>_xlfn.XLOOKUP(R4,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
         <v>0</v>
       </c>
-      <c r="N4" s="3" t="str">
+      <c r="T4" s="3" t="str">
         <f>_xlfn.XLOOKUP(A4,Ability!A:A,Ability!B:B,"")</f>
         <v>①このモンスターが攻撃を受けた時このモンスターのatkを1上昇する。
 ②このモンスターの対応役成立時、自分フィールドのモンスター全てと自分のHPを1回復する。
@@ -1129,7 +1275,7 @@
 ④アスリート</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>104</v>
       </c>
@@ -1158,26 +1304,47 @@
         <f>_xlfn.XLOOKUP(G5,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>3</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="3">
+        <f>_xlfn.XLOOKUP(I5,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="L5" s="3">
+        <f>_xlfn.XLOOKUP(K5,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N5" s="3">
+        <f>_xlfn.XLOOKUP(M5,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O5" s="3">
         <f>_xlfn.XLOOKUP(A5,Status!A:A,Status!B:B,"")</f>
         <v>2</v>
       </c>
-      <c r="J5" s="3">
+      <c r="P5" s="3">
         <f>_xlfn.XLOOKUP(A5,Status!A:A,Status!C:C,"")</f>
         <v>5</v>
       </c>
-      <c r="K5" s="3">
+      <c r="Q5" s="3">
         <f>_xlfn.XLOOKUP(A5,Status!A:A,Status!D:D,"")</f>
         <v>10</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="R5" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="M5" s="3">
-        <f>_xlfn.XLOOKUP(L5,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+      <c r="S5" s="3">
+        <f>_xlfn.XLOOKUP(R5,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
         <v>0</v>
       </c>
-      <c r="N5" s="3" t="str">
+      <c r="T5" s="3" t="str">
         <f>_xlfn.XLOOKUP(A5,Ability!A:A,Ability!B:B,"")</f>
         <v>①召喚時、相手プレイヤーか相手モンスター1体に2ダメージ。
 ②ターン終了時、山札の上から3枚を見てスペルを1枚手札に加える。
@@ -1185,7 +1352,7 @@
 ④レベルアップ</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
         <v>105</v>
       </c>
@@ -1214,26 +1381,47 @@
         <f>_xlfn.XLOOKUP(G6,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>3</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="3">
+        <f>_xlfn.XLOOKUP(I6,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="L6" s="3">
+        <f>_xlfn.XLOOKUP(K6,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N6" s="3">
+        <f>_xlfn.XLOOKUP(M6,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O6" s="3">
         <f>_xlfn.XLOOKUP(A6,Status!A:A,Status!B:B,"")</f>
         <v>2</v>
       </c>
-      <c r="J6" s="3">
+      <c r="P6" s="3">
         <f>_xlfn.XLOOKUP(A6,Status!A:A,Status!C:C,"")</f>
         <v>8</v>
       </c>
-      <c r="K6" s="3">
+      <c r="Q6" s="3">
         <f>_xlfn.XLOOKUP(A6,Status!A:A,Status!D:D,"")</f>
         <v>12</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="R6" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="M6" s="3">
-        <f>_xlfn.XLOOKUP(L6,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+      <c r="S6" s="3">
+        <f>_xlfn.XLOOKUP(R6,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
         <v>0</v>
       </c>
-      <c r="N6" s="3" t="str">
+      <c r="T6" s="3" t="str">
         <f>_xlfn.XLOOKUP(A6,Ability!A:A,Ability!B:B,"")</f>
         <v>①ターン開始時、相手のすべてのモンスターに1ダメージ与える。
 ②ターン終了時、相手のランダムなモンスターに3ダメージ与える。
@@ -1241,7 +1429,7 @@
 ④レベルアップ</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <v>106</v>
       </c>
@@ -1270,26 +1458,47 @@
         <f>_xlfn.XLOOKUP(G7,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>3</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="3">
+        <f>_xlfn.XLOOKUP(I7,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="L7" s="3">
+        <f>_xlfn.XLOOKUP(K7,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N7" s="3">
+        <f>_xlfn.XLOOKUP(M7,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O7" s="3">
         <f>_xlfn.XLOOKUP(A7,Status!A:A,Status!B:B,"")</f>
         <v>2</v>
       </c>
-      <c r="J7" s="3">
+      <c r="P7" s="3">
         <f>_xlfn.XLOOKUP(A7,Status!A:A,Status!C:C,"")</f>
         <v>10</v>
       </c>
-      <c r="K7" s="3">
+      <c r="Q7" s="3">
         <f>_xlfn.XLOOKUP(A7,Status!A:A,Status!D:D,"")</f>
         <v>15</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="R7" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="M7" s="3">
-        <f>_xlfn.XLOOKUP(L7,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+      <c r="S7" s="3">
+        <f>_xlfn.XLOOKUP(R7,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
         <v>0</v>
       </c>
-      <c r="N7" s="3" t="str">
+      <c r="T7" s="3" t="str">
         <f>_xlfn.XLOOKUP(A7,Ability!A:A,Ability!B:B,"")</f>
         <v>①ターン開始時、自分のモンスターを1体選ぶ。このターンそのモンスターのatkを+3する。
 ②対応役成立時、カードを1枚引く。
@@ -1297,7 +1506,7 @@
 ④アスリート</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A8" s="3">
         <v>107</v>
       </c>
@@ -1326,31 +1535,52 @@
         <f>_xlfn.XLOOKUP(G8,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>4</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" s="3">
+        <f>_xlfn.XLOOKUP(I8,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="L8" s="3">
+        <f>_xlfn.XLOOKUP(K8,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N8" s="3">
+        <f>_xlfn.XLOOKUP(M8,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O8" s="3">
         <f>_xlfn.XLOOKUP(A8,Status!A:A,Status!B:B,"")</f>
         <v>2</v>
       </c>
-      <c r="J8" s="3">
+      <c r="P8" s="3">
         <f>_xlfn.XLOOKUP(A8,Status!A:A,Status!C:C,"")</f>
         <v>2</v>
       </c>
-      <c r="K8" s="3">
+      <c r="Q8" s="3">
         <f>_xlfn.XLOOKUP(A8,Status!A:A,Status!D:D,"")</f>
         <v>4</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="R8" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="M8" s="3">
-        <f>_xlfn.XLOOKUP(L8,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+      <c r="S8" s="3">
+        <f>_xlfn.XLOOKUP(R8,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
         <v>0</v>
       </c>
-      <c r="N8" s="3" t="str">
+      <c r="T8" s="3" t="str">
         <f>_xlfn.XLOOKUP(A8,Ability!A:A,Ability!B:B,"")</f>
         <v>①ターゲット集中</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A9" s="3">
         <v>108</v>
       </c>
@@ -1379,32 +1609,53 @@
         <f>_xlfn.XLOOKUP(G9,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>2</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J9" s="3">
+        <f>_xlfn.XLOOKUP(I9,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="L9" s="3">
+        <f>_xlfn.XLOOKUP(K9,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N9" s="3">
+        <f>_xlfn.XLOOKUP(M9,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O9" s="3">
         <f>_xlfn.XLOOKUP(A9,Status!A:A,Status!B:B,"")</f>
         <v>2</v>
       </c>
-      <c r="J9" s="3">
+      <c r="P9" s="3">
         <f>_xlfn.XLOOKUP(A9,Status!A:A,Status!C:C,"")</f>
         <v>6</v>
       </c>
-      <c r="K9" s="3">
+      <c r="Q9" s="3">
         <f>_xlfn.XLOOKUP(A9,Status!A:A,Status!D:D,"")</f>
         <v>10</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="R9" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="M9" s="3">
-        <f>_xlfn.XLOOKUP(L9,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+      <c r="S9" s="3">
+        <f>_xlfn.XLOOKUP(R9,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
         <v>0</v>
       </c>
-      <c r="N9" s="3" t="str">
+      <c r="T9" s="3" t="str">
         <f>_xlfn.XLOOKUP(A9,Ability!A:A,Ability!B:B,"")</f>
         <v>①召喚時ランダムな敵に2ダメージ
 ②アスリート</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A10" s="3">
         <v>109</v>
       </c>
@@ -1433,31 +1684,52 @@
         <f>_xlfn.XLOOKUP(G10,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>1</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J10" s="3">
+        <f>_xlfn.XLOOKUP(I10,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="L10" s="3">
+        <f>_xlfn.XLOOKUP(K10,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N10" s="3">
+        <f>_xlfn.XLOOKUP(M10,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O10" s="3">
         <f>_xlfn.XLOOKUP(A10,Status!A:A,Status!B:B,"")</f>
         <v>2</v>
       </c>
-      <c r="J10" s="3">
+      <c r="P10" s="3">
         <f>_xlfn.XLOOKUP(A10,Status!A:A,Status!C:C,"")</f>
         <v>4</v>
       </c>
-      <c r="K10" s="3">
+      <c r="Q10" s="3">
         <f>_xlfn.XLOOKUP(A10,Status!A:A,Status!D:D,"")</f>
         <v>10</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="R10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="M10" s="3">
-        <f>_xlfn.XLOOKUP(L10,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+      <c r="S10" s="3">
+        <f>_xlfn.XLOOKUP(R10,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
         <v>0</v>
       </c>
-      <c r="N10" s="3" t="str">
+      <c r="T10" s="3" t="str">
         <f>_xlfn.XLOOKUP(A10,Ability!A:A,Ability!B:B,"")</f>
         <v>①ターン終了時、カードを1枚引く。</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A11" s="3">
         <v>110</v>
       </c>
@@ -1486,31 +1758,52 @@
         <f>_xlfn.XLOOKUP(G11,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>1</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" s="3">
+        <f>_xlfn.XLOOKUP(I11,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="L11" s="3">
+        <f>_xlfn.XLOOKUP(K11,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N11" s="3">
+        <f>_xlfn.XLOOKUP(M11,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O11" s="3">
         <f>_xlfn.XLOOKUP(A11,Status!A:A,Status!B:B,"")</f>
         <v>1</v>
       </c>
-      <c r="J11" s="3">
+      <c r="P11" s="3">
         <f>_xlfn.XLOOKUP(A11,Status!A:A,Status!C:C,"")</f>
         <v>3</v>
       </c>
-      <c r="K11" s="3">
+      <c r="Q11" s="3">
         <f>_xlfn.XLOOKUP(A11,Status!A:A,Status!D:D,"")</f>
         <v>8</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="R11" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="M11" s="3">
-        <f>_xlfn.XLOOKUP(L11,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+      <c r="S11" s="3">
+        <f>_xlfn.XLOOKUP(R11,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
         <v>0</v>
       </c>
-      <c r="N11" s="3" t="str">
+      <c r="T11" s="3" t="str">
         <f>_xlfn.XLOOKUP(A11,Ability!A:A,Ability!B:B,"")</f>
         <v>①召喚時デッキの上から3枚を見て、その中から「ロボ」モンスターを全て手札に加える。(この効果は各ターン1度しか発動しない。)</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A12" s="3">
         <v>111</v>
       </c>
@@ -1539,26 +1832,47 @@
         <f>_xlfn.XLOOKUP(G12,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>7</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J12" s="3">
+        <f>_xlfn.XLOOKUP(I12,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="L12" s="3">
+        <f>_xlfn.XLOOKUP(K12,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N12" s="3">
+        <f>_xlfn.XLOOKUP(M12,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O12" s="3">
         <f>_xlfn.XLOOKUP(A12,Status!A:A,Status!B:B,"")</f>
         <v>4</v>
       </c>
-      <c r="J12" s="3">
+      <c r="P12" s="3">
         <f>_xlfn.XLOOKUP(A12,Status!A:A,Status!C:C,"")</f>
         <v>10</v>
       </c>
-      <c r="K12" s="3">
+      <c r="Q12" s="3">
         <f>_xlfn.XLOOKUP(A12,Status!A:A,Status!D:D,"")</f>
         <v>30</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="R12" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="M12" s="3">
-        <f>_xlfn.XLOOKUP(L12,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+      <c r="S12" s="3">
+        <f>_xlfn.XLOOKUP(R12,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
         <v>0</v>
       </c>
-      <c r="N12" s="3" t="str">
+      <c r="T12" s="3" t="str">
         <f>_xlfn.XLOOKUP(A12,Ability!A:A,Ability!B:B,"")</f>
         <v>①召喚時、自分のモンスターのHPを全回復する。
 ②対応役成立時、このターンこのモンスターのatkを+5する。
@@ -1566,7 +1880,7 @@
 ④アスリート</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A13" s="3">
         <v>112</v>
       </c>
@@ -1595,26 +1909,47 @@
         <f>_xlfn.XLOOKUP(G13,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>6</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J13" s="3">
+        <f>_xlfn.XLOOKUP(I13,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="3">
+        <f>_xlfn.XLOOKUP(K13,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N13" s="3">
+        <f>_xlfn.XLOOKUP(M13,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O13" s="3">
         <f>_xlfn.XLOOKUP(A13,Status!A:A,Status!B:B,"")</f>
         <v>6</v>
       </c>
-      <c r="J13" s="3">
+      <c r="P13" s="3">
         <f>_xlfn.XLOOKUP(A13,Status!A:A,Status!C:C,"")</f>
         <v>20</v>
       </c>
-      <c r="K13" s="3">
+      <c r="Q13" s="3">
         <f>_xlfn.XLOOKUP(A13,Status!A:A,Status!D:D,"")</f>
         <v>0</v>
       </c>
-      <c r="L13" s="3" t="s">
+      <c r="R13" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="M13" s="3">
-        <f>_xlfn.XLOOKUP(L13,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+      <c r="S13" s="3">
+        <f>_xlfn.XLOOKUP(R13,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
         <v>0</v>
       </c>
-      <c r="N13" s="3" t="str">
+      <c r="T13" s="3" t="str">
         <f>_xlfn.XLOOKUP(A13,Ability!A:A,Ability!B:B,"")</f>
         <v>①相手のターン中このモンスターのatkは∞になる。
 ②このモンスターは離れない。
@@ -1622,7 +1957,7 @@
 ④反撃</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A14" s="3">
         <v>113</v>
       </c>
@@ -1651,32 +1986,53 @@
         <f>_xlfn.XLOOKUP(G14,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J14" s="3">
+        <f>_xlfn.XLOOKUP(I14,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L14" s="3">
+        <f>_xlfn.XLOOKUP(K14,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N14" s="3">
+        <f>_xlfn.XLOOKUP(M14,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O14" s="3">
         <f>_xlfn.XLOOKUP(A14,Status!A:A,Status!B:B,"")</f>
         <v>-1</v>
       </c>
-      <c r="J14" s="3">
+      <c r="P14" s="3">
         <f>_xlfn.XLOOKUP(A14,Status!A:A,Status!C:C,"")</f>
         <v>-1</v>
       </c>
-      <c r="K14" s="3">
+      <c r="Q14" s="3">
         <f>_xlfn.XLOOKUP(A14,Status!A:A,Status!D:D,"")</f>
         <v>-1</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M14" s="3">
-        <f>_xlfn.XLOOKUP(L14,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
-        <v>1</v>
-      </c>
-      <c r="N14" s="3" t="str">
+      <c r="S14" s="3">
+        <f>_xlfn.XLOOKUP(R14,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>1</v>
+      </c>
+      <c r="T14" s="3" t="str">
         <f>_xlfn.XLOOKUP(A14,Ability!A:A,Ability!B:B,"")</f>
         <v>このターンテーブルを1上昇。(この効果は各ターンに1度しか使えない)
 レベルアップ効果を持つ「RG」モンスターをレベルアップ。</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A15" s="3">
         <v>114</v>
       </c>
@@ -1705,32 +2061,53 @@
         <f>_xlfn.XLOOKUP(G15,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J15" s="3">
+        <f>_xlfn.XLOOKUP(I15,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L15" s="3">
+        <f>_xlfn.XLOOKUP(K15,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N15" s="3">
+        <f>_xlfn.XLOOKUP(M15,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O15" s="3">
         <f>_xlfn.XLOOKUP(A15,Status!A:A,Status!B:B,"")</f>
         <v>-1</v>
       </c>
-      <c r="J15" s="3">
+      <c r="P15" s="3">
         <f>_xlfn.XLOOKUP(A15,Status!A:A,Status!C:C,"")</f>
         <v>-1</v>
       </c>
-      <c r="K15" s="3">
+      <c r="Q15" s="3">
         <f>_xlfn.XLOOKUP(A15,Status!A:A,Status!D:D,"")</f>
         <v>-1</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="R15" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M15" s="3">
-        <f>_xlfn.XLOOKUP(L15,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
-        <v>1</v>
-      </c>
-      <c r="N15" s="3" t="str">
+      <c r="S15" s="3">
+        <f>_xlfn.XLOOKUP(R15,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>1</v>
+      </c>
+      <c r="T15" s="3" t="str">
         <f>_xlfn.XLOOKUP(A15,Ability!A:A,Ability!B:B,"")</f>
         <v>相手のモンスターを1体選ぶ。そのモンスターは次の相手のターンに攻撃できない。
 レベルアップ効果を持つ「RG」１体のモンスターをレベルアップ。</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A16" s="3">
         <v>115</v>
       </c>
@@ -1759,31 +2136,52 @@
         <f>_xlfn.XLOOKUP(G16,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J16" s="3">
+        <f>_xlfn.XLOOKUP(I16,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L16" s="3">
+        <f>_xlfn.XLOOKUP(K16,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N16" s="3">
+        <f>_xlfn.XLOOKUP(M16,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O16" s="3">
         <f>_xlfn.XLOOKUP(A16,Status!A:A,Status!B:B,"")</f>
         <v>-1</v>
       </c>
-      <c r="J16" s="3">
+      <c r="P16" s="3">
         <f>_xlfn.XLOOKUP(A16,Status!A:A,Status!C:C,"")</f>
         <v>-1</v>
       </c>
-      <c r="K16" s="3">
+      <c r="Q16" s="3">
         <f>_xlfn.XLOOKUP(A16,Status!A:A,Status!D:D,"")</f>
         <v>-1</v>
       </c>
-      <c r="L16" s="3" t="s">
+      <c r="R16" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M16" s="3">
-        <f>_xlfn.XLOOKUP(L16,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
-        <v>1</v>
-      </c>
-      <c r="N16" s="3" t="str">
+      <c r="S16" s="3">
+        <f>_xlfn.XLOOKUP(R16,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>1</v>
+      </c>
+      <c r="T16" s="3" t="str">
         <f>_xlfn.XLOOKUP(A16,Ability!A:A,Ability!B:B,"")</f>
         <v>次の自分のターンまでモンスター1体に「ターゲット集中」を与える。</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A17" s="3">
         <v>116</v>
       </c>
@@ -1812,31 +2210,52 @@
         <f>_xlfn.XLOOKUP(G17,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J17" s="3">
+        <f>_xlfn.XLOOKUP(I17,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L17" s="3">
+        <f>_xlfn.XLOOKUP(K17,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N17" s="3">
+        <f>_xlfn.XLOOKUP(M17,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O17" s="3">
         <f>_xlfn.XLOOKUP(A17,Status!A:A,Status!B:B,"")</f>
         <v>-1</v>
       </c>
-      <c r="J17" s="3">
+      <c r="P17" s="3">
         <f>_xlfn.XLOOKUP(A17,Status!A:A,Status!C:C,"")</f>
         <v>-1</v>
       </c>
-      <c r="K17" s="3">
+      <c r="Q17" s="3">
         <f>_xlfn.XLOOKUP(A17,Status!A:A,Status!D:D,"")</f>
         <v>-1</v>
       </c>
-      <c r="L17" s="3" t="s">
+      <c r="R17" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M17" s="3">
-        <f>_xlfn.XLOOKUP(L17,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
-        <v>1</v>
-      </c>
-      <c r="N17" s="3" t="str">
+      <c r="S17" s="3">
+        <f>_xlfn.XLOOKUP(R17,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>1</v>
+      </c>
+      <c r="T17" s="3" t="str">
         <f>_xlfn.XLOOKUP(A17,Ability!A:A,Ability!B:B,"")</f>
         <v>自分のサイズ2以下のモンスターを1体選ぶ。次の自分のターンまでそのモンスターは対応役成立につき2回攻撃する。</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A18" s="3">
         <v>117</v>
       </c>
@@ -1865,31 +2284,52 @@
         <f>_xlfn.XLOOKUP(G18,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J18" s="3">
+        <f>_xlfn.XLOOKUP(I18,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="L18" s="3">
+        <f>_xlfn.XLOOKUP(K18,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N18" s="3">
+        <f>_xlfn.XLOOKUP(M18,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O18" s="3">
         <f>_xlfn.XLOOKUP(A18,Status!A:A,Status!B:B,"")</f>
         <v>-1</v>
       </c>
-      <c r="J18" s="3">
+      <c r="P18" s="3">
         <f>_xlfn.XLOOKUP(A18,Status!A:A,Status!C:C,"")</f>
         <v>-1</v>
       </c>
-      <c r="K18" s="3">
+      <c r="Q18" s="3">
         <f>_xlfn.XLOOKUP(A18,Status!A:A,Status!D:D,"")</f>
         <v>-1</v>
       </c>
-      <c r="L18" s="3" t="s">
+      <c r="R18" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M18" s="3">
-        <f>_xlfn.XLOOKUP(L18,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
-        <v>1</v>
-      </c>
-      <c r="N18" s="3" t="str">
+      <c r="S18" s="3">
+        <f>_xlfn.XLOOKUP(R18,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>1</v>
+      </c>
+      <c r="T18" s="3" t="str">
         <f>_xlfn.XLOOKUP(A18,Ability!A:A,Ability!B:B,"")</f>
         <v>山札の上から7枚見て「ロボ」を種族に含むモンスターを手札に加える。(この効果は各ターンに1度しか使えない)</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A19" s="3">
         <v>118</v>
       </c>
@@ -1918,31 +2358,52 @@
         <f>_xlfn.XLOOKUP(G19,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J19" s="3">
+        <f>_xlfn.XLOOKUP(I19,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="L19" s="3">
+        <f>_xlfn.XLOOKUP(K19,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N19" s="3">
+        <f>_xlfn.XLOOKUP(M19,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O19" s="3">
         <f>_xlfn.XLOOKUP(A19,Status!A:A,Status!B:B,"")</f>
         <v>-1</v>
       </c>
-      <c r="J19" s="3">
+      <c r="P19" s="3">
         <f>_xlfn.XLOOKUP(A19,Status!A:A,Status!C:C,"")</f>
         <v>-1</v>
       </c>
-      <c r="K19" s="3">
+      <c r="Q19" s="3">
         <f>_xlfn.XLOOKUP(A19,Status!A:A,Status!D:D,"")</f>
         <v>-1</v>
       </c>
-      <c r="L19" s="3" t="s">
+      <c r="R19" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M19" s="3">
-        <f>_xlfn.XLOOKUP(L19,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
-        <v>1</v>
-      </c>
-      <c r="N19" s="3" t="str">
+      <c r="S19" s="3">
+        <f>_xlfn.XLOOKUP(R19,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>1</v>
+      </c>
+      <c r="T19" s="3" t="str">
         <f>_xlfn.XLOOKUP(A19,Ability!A:A,Ability!B:B,"")</f>
         <v>「RG」を名称に含むモンスターのレベルを上げる。</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A20" s="3">
         <v>119</v>
       </c>
@@ -1971,31 +2432,52 @@
         <f>_xlfn.XLOOKUP(G20,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>0</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J20" s="3">
+        <f>_xlfn.XLOOKUP(I20,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="L20" s="3">
+        <f>_xlfn.XLOOKUP(K20,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N20" s="3">
+        <f>_xlfn.XLOOKUP(M20,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O20" s="3">
         <f>_xlfn.XLOOKUP(A20,Status!A:A,Status!B:B,"")</f>
         <v>-1</v>
       </c>
-      <c r="J20" s="3">
+      <c r="P20" s="3">
         <f>_xlfn.XLOOKUP(A20,Status!A:A,Status!C:C,"")</f>
         <v>-1</v>
       </c>
-      <c r="K20" s="3">
+      <c r="Q20" s="3">
         <f>_xlfn.XLOOKUP(A20,Status!A:A,Status!D:D,"")</f>
         <v>-1</v>
       </c>
-      <c r="L20" s="3" t="s">
+      <c r="R20" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M20" s="3">
-        <f>_xlfn.XLOOKUP(L20,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
-        <v>1</v>
-      </c>
-      <c r="N20" s="3" t="str">
+      <c r="S20" s="3">
+        <f>_xlfn.XLOOKUP(R20,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>1</v>
+      </c>
+      <c r="T20" s="3" t="str">
         <f>_xlfn.XLOOKUP(A20,Ability!A:A,Ability!B:B,"")</f>
         <v>自分のモンスターを1体選ぶ。そのモンスターは次の自分のターンまで、受けるダメージを-2する。</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A21" s="3">
         <v>120</v>
       </c>
@@ -2024,31 +2506,52 @@
         <f>_xlfn.XLOOKUP(G21,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>0</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J21" s="3">
+        <f>_xlfn.XLOOKUP(I21,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="L21" s="3">
+        <f>_xlfn.XLOOKUP(K21,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N21" s="3">
+        <f>_xlfn.XLOOKUP(M21,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O21" s="3">
         <f>_xlfn.XLOOKUP(A21,Status!A:A,Status!B:B,"")</f>
         <v>-1</v>
       </c>
-      <c r="J21" s="3">
+      <c r="P21" s="3">
         <f>_xlfn.XLOOKUP(A21,Status!A:A,Status!C:C,"")</f>
         <v>-1</v>
       </c>
-      <c r="K21" s="3">
+      <c r="Q21" s="3">
         <f>_xlfn.XLOOKUP(A21,Status!A:A,Status!D:D,"")</f>
         <v>-1</v>
       </c>
-      <c r="L21" s="3" t="s">
+      <c r="R21" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M21" s="3">
-        <f>_xlfn.XLOOKUP(L21,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
-        <v>1</v>
-      </c>
-      <c r="N21" s="3" t="str">
+      <c r="S21" s="3">
+        <f>_xlfn.XLOOKUP(R21,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>1</v>
+      </c>
+      <c r="T21" s="3" t="str">
         <f>_xlfn.XLOOKUP(A21,Ability!A:A,Ability!B:B,"")</f>
         <v>墓地からatk4以下のモンスターを出す</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A22" s="3">
         <v>121</v>
       </c>
@@ -2077,31 +2580,52 @@
         <f>_xlfn.XLOOKUP(G22,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J22" s="3">
+        <f>_xlfn.XLOOKUP(I22,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L22" s="3">
+        <f>_xlfn.XLOOKUP(K22,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N22" s="3">
+        <f>_xlfn.XLOOKUP(M22,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O22" s="3">
         <f>_xlfn.XLOOKUP(A22,Status!A:A,Status!B:B,"")</f>
         <v>-1</v>
       </c>
-      <c r="J22" s="3">
+      <c r="P22" s="3">
         <f>_xlfn.XLOOKUP(A22,Status!A:A,Status!C:C,"")</f>
         <v>-1</v>
       </c>
-      <c r="K22" s="3">
+      <c r="Q22" s="3">
         <f>_xlfn.XLOOKUP(A22,Status!A:A,Status!D:D,"")</f>
         <v>-1</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="R22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M22" s="3">
-        <f>_xlfn.XLOOKUP(L22,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
-        <v>1</v>
-      </c>
-      <c r="N22" s="3" t="str">
+      <c r="S22" s="3">
+        <f>_xlfn.XLOOKUP(R22,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>1</v>
+      </c>
+      <c r="T22" s="3" t="str">
         <f>_xlfn.XLOOKUP(A22,Ability!A:A,Ability!B:B,"")</f>
         <v>カードを2枚引く。(この効果は各ターンに1度しか使えない)</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A23" s="3">
         <v>122</v>
       </c>
@@ -2130,31 +2654,52 @@
         <f>_xlfn.XLOOKUP(G23,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="3">
+      <c r="I23" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J23" s="3">
+        <f>_xlfn.XLOOKUP(I23,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L23" s="3">
+        <f>_xlfn.XLOOKUP(K23,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N23" s="3">
+        <f>_xlfn.XLOOKUP(M23,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="O23" s="3">
         <f>_xlfn.XLOOKUP(A23,Status!A:A,Status!B:B,"")</f>
         <v>-1</v>
       </c>
-      <c r="J23" s="3">
+      <c r="P23" s="3">
         <f>_xlfn.XLOOKUP(A23,Status!A:A,Status!C:C,"")</f>
         <v>-1</v>
       </c>
-      <c r="K23" s="3">
+      <c r="Q23" s="3">
         <f>_xlfn.XLOOKUP(A23,Status!A:A,Status!D:D,"")</f>
         <v>-1</v>
       </c>
-      <c r="L23" s="3" t="s">
+      <c r="R23" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M23" s="3">
-        <f>_xlfn.XLOOKUP(L23,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
-        <v>1</v>
-      </c>
-      <c r="N23" s="3" t="str">
+      <c r="S23" s="3">
+        <f>_xlfn.XLOOKUP(R23,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
+        <v>1</v>
+      </c>
+      <c r="T23" s="3" t="str">
         <f>_xlfn.XLOOKUP(A23,Ability!A:A,Ability!B:B,"")</f>
         <v>相手のすべてのモンスターに2ダメージを与える</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A24" s="3">
         <v>201</v>
       </c>
@@ -2174,8 +2719,14 @@
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A25" s="3">
         <v>202</v>
       </c>
@@ -2195,8 +2746,14 @@
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A26" s="3">
         <v>203</v>
       </c>
@@ -2216,8 +2773,14 @@
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A27" s="3">
         <v>204</v>
       </c>
@@ -2237,8 +2800,14 @@
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A28" s="3">
         <v>205</v>
       </c>
@@ -2258,8 +2827,14 @@
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A29" s="3">
         <v>206</v>
       </c>
@@ -2279,8 +2854,14 @@
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A30" s="3">
         <v>207</v>
       </c>
@@ -2300,6 +2881,12 @@
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -2312,7 +2899,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FB6E8B83-655D-43E5-9D49-125D76F5837E}">
           <x14:formula1>
             <xm:f>Rarity!$B$2:$B$6</xm:f>
@@ -2329,7 +2916,7 @@
           <x14:formula1>
             <xm:f>Type!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>L2:L23</xm:sqref>
+          <xm:sqref>R2:R23</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1B3501F0-A3BC-49B7-9401-98C97ACDC1EF}">
           <x14:formula1>
@@ -2342,6 +2929,12 @@
             <xm:f>Koyaku!$B$2:$B$9</xm:f>
           </x14:formula1>
           <xm:sqref>G2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B52A84D4-369B-4405-B560-372E5EF1A995}">
+          <x14:formula1>
+            <xm:f>Race!$B$2:$B$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>I2:I23 K2:K23 M2:M23</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3346,6 +3939,58 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0568C38A-56C9-490E-B529-9128DA20C98A}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" s="3">
+        <v>-1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" s="3">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A11AEFB-2CB3-4B10-99EE-D988C439CE1A}">
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>

--- a/Assets/Resources/MasterData/CardData.xlsx
+++ b/Assets/Resources/MasterData/CardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REBIRTH_GENESIS\3DTest\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F709B37-ACE1-49C9-B279-1EB9FAB27046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61FA0B1E-7DFE-4BA1-A4DB-0E878D42C844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8D1AA26D-1EB1-44B6-9ABB-10521DDCFE30}"/>
+    <workbookView xWindow="5520" yWindow="-13365" windowWidth="21600" windowHeight="11295" xr2:uid="{8D1AA26D-1EB1-44B6-9ABB-10521DDCFE30}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="106">
   <si>
     <t>themeID</t>
     <phoneticPr fontId="2"/>
@@ -487,6 +487,10 @@
   </si>
   <si>
     <t>ThildRaceID</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>CardType</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -981,7 +985,7 @@
     <col min="12" max="12" width="14.375" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="14.375" customWidth="1"/>
     <col min="18" max="18" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="205.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1041,7 +1045,7 @@
         <v>88</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>86</v>

--- a/Assets/Resources/MasterData/CardData.xlsx
+++ b/Assets/Resources/MasterData/CardData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REBIRTH_GENESIS\3DTest\Assets\Resources\MasterData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student3\Documents\GitHub\3DTest\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61FA0B1E-7DFE-4BA1-A4DB-0E878D42C844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F447783C-4B52-4282-91FF-D536E4D30680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5520" yWindow="-13365" windowWidth="21600" windowHeight="11295" xr2:uid="{8D1AA26D-1EB1-44B6-9ABB-10521DDCFE30}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8D1AA26D-1EB1-44B6-9ABB-10521DDCFE30}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -121,9 +121,6 @@
     <t>リプレイウィング</t>
   </si>
   <si>
-    <t>AIP　χ‐S</t>
-  </si>
-  <si>
     <t>AIP　CH=RAY</t>
   </si>
   <si>
@@ -491,6 +488,10 @@
   </si>
   <si>
     <t>CardType</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>AIP　χ=S</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -994,61 +995,61 @@
         <v>2</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="I1" s="14" t="s">
-        <v>94</v>
-      </c>
       <c r="J1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="L1" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="N1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R1" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R1" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="T1" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.4">
@@ -1060,42 +1061,42 @@
         <v>RG:ISUKA LV1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3">
         <f>_xlfn.XLOOKUP(C2,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F2" s="3">
         <f>_xlfn.XLOOKUP(E2,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H2" s="3">
         <f>_xlfn.XLOOKUP(G2,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>5</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J2" s="3">
         <f>_xlfn.XLOOKUP(I2,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L2" s="3">
         <f>_xlfn.XLOOKUP(K2,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N2" s="3">
         <f>_xlfn.XLOOKUP(M2,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1114,7 +1115,7 @@
         <v>11</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S2" s="3">
         <f>_xlfn.XLOOKUP(R2,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1135,42 +1136,42 @@
         <v>RG:ISUKA LV2</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D3" s="3">
         <f>_xlfn.XLOOKUP(C3,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>-1</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F3" s="3">
         <f>_xlfn.XLOOKUP(E3,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H3" s="3">
         <f>_xlfn.XLOOKUP(G3,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>5</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J3" s="3">
         <f>_xlfn.XLOOKUP(I3,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L3" s="3">
         <f>_xlfn.XLOOKUP(K3,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N3" s="3">
         <f>_xlfn.XLOOKUP(M3,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1189,7 +1190,7 @@
         <v>14</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S3" s="3">
         <f>_xlfn.XLOOKUP(R3,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1211,42 +1212,42 @@
         <v>RG:ISUKA LV3</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="3">
         <f>_xlfn.XLOOKUP(C4,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>-1</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F4" s="3">
         <f>_xlfn.XLOOKUP(E4,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H4" s="3">
         <f>_xlfn.XLOOKUP(G4,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>5</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J4" s="3">
         <f>_xlfn.XLOOKUP(I4,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L4" s="3">
         <f>_xlfn.XLOOKUP(K4,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N4" s="3">
         <f>_xlfn.XLOOKUP(M4,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1265,7 +1266,7 @@
         <v>17</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S4" s="3">
         <f>_xlfn.XLOOKUP(R4,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1288,42 +1289,42 @@
         <v>RG:REACHE Lv.1</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3">
         <f>_xlfn.XLOOKUP(C5,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F5" s="3">
         <f>_xlfn.XLOOKUP(E5,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H5" s="3">
         <f>_xlfn.XLOOKUP(G5,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>3</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J5" s="3">
         <f>_xlfn.XLOOKUP(I5,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L5" s="3">
         <f>_xlfn.XLOOKUP(K5,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N5" s="3">
         <f>_xlfn.XLOOKUP(M5,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1342,7 +1343,7 @@
         <v>10</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S5" s="3">
         <f>_xlfn.XLOOKUP(R5,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1365,42 +1366,42 @@
         <v>RG:REACHE Lv.2</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6" s="3">
         <f>_xlfn.XLOOKUP(C6,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>-1</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F6" s="3">
         <f>_xlfn.XLOOKUP(E6,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H6" s="3">
         <f>_xlfn.XLOOKUP(G6,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>3</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J6" s="3">
         <f>_xlfn.XLOOKUP(I6,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L6" s="3">
         <f>_xlfn.XLOOKUP(K6,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N6" s="3">
         <f>_xlfn.XLOOKUP(M6,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1419,7 +1420,7 @@
         <v>12</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S6" s="3">
         <f>_xlfn.XLOOKUP(R6,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1442,42 +1443,42 @@
         <v>RG:REACHE Lv.3</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" s="3">
         <f>_xlfn.XLOOKUP(C7,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>-1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F7" s="3">
         <f>_xlfn.XLOOKUP(E7,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H7" s="3">
         <f>_xlfn.XLOOKUP(G7,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>3</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J7" s="3">
         <f>_xlfn.XLOOKUP(I7,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L7" s="3">
         <f>_xlfn.XLOOKUP(K7,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N7" s="3">
         <f>_xlfn.XLOOKUP(M7,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1496,7 +1497,7 @@
         <v>15</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S7" s="3">
         <f>_xlfn.XLOOKUP(R7,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1519,42 +1520,42 @@
         <v>RG:BELL</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" s="3">
         <f>_xlfn.XLOOKUP(C8,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F8" s="3">
         <f>_xlfn.XLOOKUP(E8,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H8" s="3">
         <f>_xlfn.XLOOKUP(G8,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>4</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J8" s="3">
         <f>_xlfn.XLOOKUP(I8,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L8" s="3">
         <f>_xlfn.XLOOKUP(K8,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N8" s="3">
         <f>_xlfn.XLOOKUP(M8,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1573,7 +1574,7 @@
         <v>4</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S8" s="3">
         <f>_xlfn.XLOOKUP(R8,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1593,42 +1594,42 @@
         <v>RG:REI</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D9" s="3">
         <f>_xlfn.XLOOKUP(C9,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F9" s="3">
         <f>_xlfn.XLOOKUP(E9,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H9" s="3">
         <f>_xlfn.XLOOKUP(G9,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>2</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J9" s="3">
         <f>_xlfn.XLOOKUP(I9,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L9" s="3">
         <f>_xlfn.XLOOKUP(K9,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N9" s="3">
         <f>_xlfn.XLOOKUP(M9,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1647,7 +1648,7 @@
         <v>10</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S9" s="3">
         <f>_xlfn.XLOOKUP(R9,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1668,42 +1669,42 @@
         <v>RG:LANK</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" s="3">
         <f>_xlfn.XLOOKUP(C10,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>2</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F10" s="3">
         <f>_xlfn.XLOOKUP(E10,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H10" s="3">
         <f>_xlfn.XLOOKUP(G10,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>1</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J10" s="3">
         <f>_xlfn.XLOOKUP(I10,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L10" s="3">
         <f>_xlfn.XLOOKUP(K10,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N10" s="3">
         <f>_xlfn.XLOOKUP(M10,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1722,7 +1723,7 @@
         <v>10</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S10" s="3">
         <f>_xlfn.XLOOKUP(R10,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1742,42 +1743,42 @@
         <v>Raymond Blank</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" s="3">
         <f>_xlfn.XLOOKUP(C11,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>3</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F11" s="3">
         <f>_xlfn.XLOOKUP(E11,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H11" s="3">
         <f>_xlfn.XLOOKUP(G11,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>1</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J11" s="3">
         <f>_xlfn.XLOOKUP(I11,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L11" s="3">
         <f>_xlfn.XLOOKUP(K11,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>3</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N11" s="3">
         <f>_xlfn.XLOOKUP(M11,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1796,7 +1797,7 @@
         <v>8</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S11" s="3">
         <f>_xlfn.XLOOKUP(R11,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1816,42 +1817,42 @@
         <v>RG:IRIS</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D12" s="3">
         <f>_xlfn.XLOOKUP(C12,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>-1</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F12" s="3">
         <f>_xlfn.XLOOKUP(E12,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H12" s="3">
         <f>_xlfn.XLOOKUP(G12,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>7</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J12" s="3">
         <f>_xlfn.XLOOKUP(I12,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L12" s="3">
         <f>_xlfn.XLOOKUP(K12,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N12" s="3">
         <f>_xlfn.XLOOKUP(M12,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1870,7 +1871,7 @@
         <v>30</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S12" s="3">
         <f>_xlfn.XLOOKUP(R12,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1893,42 +1894,42 @@
         <v>RG:REICHELS</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" s="3">
         <f>_xlfn.XLOOKUP(C13,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>-1</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F13" s="3">
         <f>_xlfn.XLOOKUP(E13,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H13" s="3">
         <f>_xlfn.XLOOKUP(G13,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>6</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J13" s="3">
         <f>_xlfn.XLOOKUP(I13,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L13" s="3">
         <f>_xlfn.XLOOKUP(K13,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N13" s="3">
         <f>_xlfn.XLOOKUP(M13,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1947,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S13" s="3">
         <f>_xlfn.XLOOKUP(R13,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1970,42 +1971,42 @@
         <v>スイカブラスター</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D14" s="3">
         <f>_xlfn.XLOOKUP(C14,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>3</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F14" s="3">
         <f>_xlfn.XLOOKUP(E14,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H14" s="3">
         <f>_xlfn.XLOOKUP(G14,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J14" s="3">
         <f>_xlfn.XLOOKUP(I14,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L14" s="3">
         <f>_xlfn.XLOOKUP(K14,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N14" s="3">
         <f>_xlfn.XLOOKUP(M14,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -2024,7 +2025,7 @@
         <v>-1</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S14" s="3">
         <f>_xlfn.XLOOKUP(R14,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2045,42 +2046,42 @@
         <v>サイバーチェリー</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" s="3">
         <f>_xlfn.XLOOKUP(C15,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>3</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F15" s="3">
         <f>_xlfn.XLOOKUP(E15,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H15" s="3">
         <f>_xlfn.XLOOKUP(G15,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>0</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J15" s="3">
         <f>_xlfn.XLOOKUP(I15,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L15" s="3">
         <f>_xlfn.XLOOKUP(K15,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N15" s="3">
         <f>_xlfn.XLOOKUP(M15,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -2099,7 +2100,7 @@
         <v>-1</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S15" s="3">
         <f>_xlfn.XLOOKUP(R15,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2120,42 +2121,42 @@
         <v>ベルギア</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" s="3">
         <f>_xlfn.XLOOKUP(C16,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>3</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F16" s="3">
         <f>_xlfn.XLOOKUP(E16,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H16" s="3">
         <f>_xlfn.XLOOKUP(G16,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>0</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J16" s="3">
         <f>_xlfn.XLOOKUP(I16,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L16" s="3">
         <f>_xlfn.XLOOKUP(K16,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N16" s="3">
         <f>_xlfn.XLOOKUP(M16,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -2174,7 +2175,7 @@
         <v>-1</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S16" s="3">
         <f>_xlfn.XLOOKUP(R16,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2194,42 +2195,42 @@
         <v>リプレイウィング</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" s="3">
         <f>_xlfn.XLOOKUP(C17,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>3</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F17" s="3">
         <f>_xlfn.XLOOKUP(E17,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H17" s="3">
         <f>_xlfn.XLOOKUP(G17,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>0</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J17" s="3">
         <f>_xlfn.XLOOKUP(I17,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L17" s="3">
         <f>_xlfn.XLOOKUP(K17,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N17" s="3">
         <f>_xlfn.XLOOKUP(M17,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -2248,7 +2249,7 @@
         <v>-1</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S17" s="3">
         <f>_xlfn.XLOOKUP(R17,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2265,45 +2266,45 @@
       </c>
       <c r="B18" s="5" t="str">
         <f>_xlfn.XLOOKUP(A18,Name!A:A,Name!B:B,"")</f>
-        <v>AIP　χ‐S</v>
+        <v>AIP　χ=S</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18" s="3">
         <f>_xlfn.XLOOKUP(C18,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>2</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F18" s="3">
         <f>_xlfn.XLOOKUP(E18,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H18" s="3">
         <f>_xlfn.XLOOKUP(G18,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>0</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J18" s="3">
         <f>_xlfn.XLOOKUP(I18,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L18" s="3">
         <f>_xlfn.XLOOKUP(K18,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>3</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N18" s="3">
         <f>_xlfn.XLOOKUP(M18,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -2322,7 +2323,7 @@
         <v>-1</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S18" s="3">
         <f>_xlfn.XLOOKUP(R18,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2342,42 +2343,42 @@
         <v>AIP　CH=RAY</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" s="3">
         <f>_xlfn.XLOOKUP(C19,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>2</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F19" s="3">
         <f>_xlfn.XLOOKUP(E19,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H19" s="3">
         <f>_xlfn.XLOOKUP(G19,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>0</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J19" s="3">
         <f>_xlfn.XLOOKUP(I19,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L19" s="3">
         <f>_xlfn.XLOOKUP(K19,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>3</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N19" s="3">
         <f>_xlfn.XLOOKUP(M19,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -2396,7 +2397,7 @@
         <v>-1</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S19" s="3">
         <f>_xlfn.XLOOKUP(R19,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2416,42 +2417,42 @@
         <v>AIP　VAIL=Δ</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D20" s="3">
         <f>_xlfn.XLOOKUP(C20,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>2</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F20" s="3">
         <f>_xlfn.XLOOKUP(E20,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H20" s="3">
         <f>_xlfn.XLOOKUP(G20,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>0</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J20" s="3">
         <f>_xlfn.XLOOKUP(I20,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L20" s="3">
         <f>_xlfn.XLOOKUP(K20,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>3</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N20" s="3">
         <f>_xlfn.XLOOKUP(M20,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -2470,7 +2471,7 @@
         <v>-1</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S20" s="3">
         <f>_xlfn.XLOOKUP(R20,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2490,42 +2491,42 @@
         <v>AIP　RERAY=0</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21" s="3">
         <f>_xlfn.XLOOKUP(C21,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>2</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F21" s="3">
         <f>_xlfn.XLOOKUP(E21,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H21" s="3">
         <f>_xlfn.XLOOKUP(G21,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>0</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J21" s="3">
         <f>_xlfn.XLOOKUP(I21,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L21" s="3">
         <f>_xlfn.XLOOKUP(K21,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>3</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N21" s="3">
         <f>_xlfn.XLOOKUP(M21,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -2544,7 +2545,7 @@
         <v>-1</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S21" s="3">
         <f>_xlfn.XLOOKUP(R21,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2564,42 +2565,42 @@
         <v>REEL・SLIP</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D22" s="3">
         <f>_xlfn.XLOOKUP(C22,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>2</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F22" s="3">
         <f>_xlfn.XLOOKUP(E22,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H22" s="3">
         <f>_xlfn.XLOOKUP(G22,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J22" s="3">
         <f>_xlfn.XLOOKUP(I22,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L22" s="3">
         <f>_xlfn.XLOOKUP(K22,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N22" s="3">
         <f>_xlfn.XLOOKUP(M22,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -2618,7 +2619,7 @@
         <v>-1</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S22" s="3">
         <f>_xlfn.XLOOKUP(R22,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2638,42 +2639,42 @@
         <v>PERFECT　STOP</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D23" s="3">
         <f>_xlfn.XLOOKUP(C23,Rarity!$B$2:$B$6,Rarity!$A$2:$A$6,"")</f>
         <v>2</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F23" s="3">
         <f>_xlfn.XLOOKUP(E23,Theme!$B$2:$B$6,Theme!$A$2:$A$6,"")</f>
         <v>1</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H23" s="3">
         <f>_xlfn.XLOOKUP(G23,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
         <v>0</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J23" s="3">
         <f>_xlfn.XLOOKUP(I23,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>1</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L23" s="3">
         <f>_xlfn.XLOOKUP(K23,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N23" s="3">
         <f>_xlfn.XLOOKUP(M23,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -2692,7 +2693,7 @@
         <v>-1</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S23" s="3">
         <f>_xlfn.XLOOKUP(R23,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2959,7 +2960,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
@@ -2967,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
@@ -2975,7 +2976,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -3150,7 +3151,7 @@
         <v>117</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
@@ -3159,7 +3160,7 @@
         <v>118</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
@@ -3168,7 +3169,7 @@
         <v>119</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
@@ -3177,7 +3178,7 @@
         <v>120</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
@@ -3186,7 +3187,7 @@
         <v>121</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
@@ -3195,7 +3196,7 @@
         <v>122</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
@@ -3250,6 +3251,7 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3263,7 +3265,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
@@ -3271,7 +3273,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
@@ -3279,7 +3281,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
@@ -3287,7 +3289,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
@@ -3295,7 +3297,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
@@ -3303,7 +3305,7 @@
         <v>-1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -3323,7 +3325,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
@@ -3331,7 +3333,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
@@ -3339,7 +3341,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
@@ -3379,7 +3381,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="37.5" x14ac:dyDescent="0.4">
@@ -3388,7 +3390,7 @@
         <v>101</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="56.25" x14ac:dyDescent="0.4">
@@ -3397,7 +3399,7 @@
         <v>102</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="75" x14ac:dyDescent="0.4">
@@ -3406,7 +3408,7 @@
         <v>103</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.4">
@@ -3415,7 +3417,7 @@
         <v>104</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.4">
@@ -3424,7 +3426,7 @@
         <v>105</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="75" x14ac:dyDescent="0.4">
@@ -3433,7 +3435,7 @@
         <v>106</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
@@ -3442,7 +3444,7 @@
         <v>107</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="37.5" x14ac:dyDescent="0.4">
@@ -3451,7 +3453,7 @@
         <v>108</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
@@ -3460,7 +3462,7 @@
         <v>109</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
@@ -3469,7 +3471,7 @@
         <v>110</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="75" x14ac:dyDescent="0.4">
@@ -3478,7 +3480,7 @@
         <v>111</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="75" x14ac:dyDescent="0.4">
@@ -3487,7 +3489,7 @@
         <v>112</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="37.5" x14ac:dyDescent="0.4">
@@ -3496,7 +3498,7 @@
         <v>113</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="37.5" x14ac:dyDescent="0.4">
@@ -3505,7 +3507,7 @@
         <v>114</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
@@ -3514,7 +3516,7 @@
         <v>115</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
@@ -3523,7 +3525,7 @@
         <v>116</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
@@ -3532,7 +3534,7 @@
         <v>117</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
@@ -3541,7 +3543,7 @@
         <v>118</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
@@ -3550,7 +3552,7 @@
         <v>119</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
@@ -3559,7 +3561,7 @@
         <v>120</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
@@ -3568,7 +3570,7 @@
         <v>121</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
@@ -3577,7 +3579,7 @@
         <v>122</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -3596,13 +3598,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
@@ -3952,7 +3954,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
@@ -3960,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
@@ -3968,7 +3970,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
@@ -3976,7 +3978,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
@@ -3984,7 +3986,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -4007,7 +4009,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
@@ -4015,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
@@ -4023,7 +4025,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
@@ -4031,7 +4033,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
@@ -4039,7 +4041,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
@@ -4047,7 +4049,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
@@ -4055,7 +4057,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
@@ -4063,7 +4065,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
@@ -4071,7 +4073,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/MasterData/CardData.xlsx
+++ b/Assets/Resources/MasterData/CardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student3\Documents\GitHub\3DTest\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F447783C-4B52-4282-91FF-D536E4D30680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70745722-66B2-4E7E-B05F-C96DF2082842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8D1AA26D-1EB1-44B6-9ABB-10521DDCFE30}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{8D1AA26D-1EB1-44B6-9ABB-10521DDCFE30}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -220,118 +220,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>①召喚時、手札を1枚捨ててもよい。そうしたら山札の上から5枚見て、種族に「ロボ」を含むカードを１枚手札に加える。
-②レベルアップ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>①ターン終了時プレイヤーのHPを2回復する。
-②このモンスターが攻撃を受けた時このモンスターのHPを1回復する。
-③レベルアップ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>①このモンスターが攻撃を受けた時このモンスターのatkを1上昇する。
-②このモンスターの対応役成立時、自分フィールドのモンスター全てと自分のHPを1回復する。
-③このモンスターは効果で破壊されない
-④アスリート</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>①召喚時、相手プレイヤーか相手モンスター1体に2ダメージ。
-②ターン終了時、山札の上から3枚を見てスペルを1枚手札に加える。
-③アスリート
-④レベルアップ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>①ターン開始時、相手のすべてのモンスターに1ダメージ与える。
-②ターン終了時、相手のランダムなモンスターに3ダメージ与える。
-③アスリート
-④レベルアップ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>①ターン開始時、自分のモンスターを1体選ぶ。このターンそのモンスターのatkを+3する。
-②対応役成立時、カードを1枚引く。
-③このモンスターは効果で破壊されない。
-④アスリート</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>①ターゲット集中</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>①召喚時ランダムな敵に2ダメージ
-②アスリート</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>①ターン終了時、カードを1枚引く。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>①召喚時デッキの上から3枚を見て、その中から「ロボ」モンスターを全て手札に加える。(この効果は各ターン1度しか発動しない。)</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>①召喚時、自分のモンスターのHPを全回復する。
-②対応役成立時、このターンこのモンスターのatkを+5する。
-③このモンスターは効果で破壊されない
-④アスリート</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>①相手のターン中このモンスターのatkは∞になる。
-②このモンスターは離れない。
-③アスリート
-④反撃</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>このターンテーブルを1上昇。(この効果は各ターンに1度しか使えない)
-レベルアップ効果を持つ「RG」モンスターをレベルアップ。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>相手のモンスターを1体選ぶ。そのモンスターは次の相手のターンに攻撃できない。
-レベルアップ効果を持つ「RG」１体のモンスターをレベルアップ。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>次の自分のターンまでモンスター1体に「ターゲット集中」を与える。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>自分のサイズ2以下のモンスターを1体選ぶ。次の自分のターンまでそのモンスターは対応役成立につき2回攻撃する。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>山札の上から7枚見て「ロボ」を種族に含むモンスターを手札に加える。(この効果は各ターンに1度しか使えない)</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>「RG」を名称に含むモンスターのレベルを上げる。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>自分のモンスターを1体選ぶ。そのモンスターは次の自分のターンまで、受けるダメージを-2する。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>墓地からatk4以下のモンスターを出す</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>カードを2枚引く。(この効果は各ターンに1度しか使えない)</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>相手のすべてのモンスターに2ダメージを与える</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>Koyaku</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -492,6 +380,118 @@
   </si>
   <si>
     <t>AIP　χ=S</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・召喚時、手札を1枚捨ててもよい。そうしたら山札の上から5枚見て、種族に「ロボ」を含むカードを１枚手札に加える。
+・レベルアップ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・ターン終了時プレイヤーのHPを2回復する。
+・このモンスターが攻撃を受けた時このモンスターのHPを1回復する。
+・レベルアップ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・このモンスターが攻撃を受けた時このモンスターのatkを1上昇する。
+・このモンスターの対応役成立時、自分フィールドのモンスター全てと自分のHPを1回復する。
+・このモンスターは効果で破壊されない
+・アスリート</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・召喚時、相手プレイヤーか相手モンスター1体に2ダメージ。
+・ターン終了時、山札の上から3枚を見てスペルを1枚手札に加える。
+・アスリート
+・レベルアップ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・ターン開始時、相手のすべてのモンスターに1ダメージ与える。
+・ターン終了時、相手のランダムなモンスターに3ダメージ与える。
+・アスリート
+・レベルアップ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・ターン開始時、自分のモンスターを1体選ぶ。このターンそのモンスターのatkを+3する。
+・対応役成立時、カードを1枚引く。
+・このモンスターは効果で破壊されない。
+・アスリート</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・ターゲット集中</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・召喚時ランダムな敵に2ダメージ
+・アスリート</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・ターン終了時、カードを1枚引く。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・召喚時デッキの上から3枚を見て、その中から「ロボ」モンスターを全て手札に加える。(この効果は各ターン1度しか発動しない。)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・召喚時、自分のモンスターのHPを全回復する。
+・対応役成立時、このターンこのモンスターのatkを+5する。
+・このモンスターは効果で破壊されない
+・アスリート</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・相手のターン中このモンスターのatkは∞になる。
+・このモンスターは離れない。
+・アスリート
+・反撃</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・このターンテーブルを1上昇。(この効果は各ターンに1度しか使えない)
+・レベルアップ効果を持つ「RG」モンスターをレベルアップ。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・相手のモンスターを1体選ぶ。そのモンスターは次の相手のターンに攻撃できない。
+・レベルアップ効果を持つ「RG」１体のモンスターをレベルアップ。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・次の自分のターンまでモンスター1体に「ターゲット集中」を与える。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・自分のサイズ2以下のモンスターを1体選ぶ。次の自分のターンまでそのモンスターは対応役成立につき2回攻撃する。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・山札の上から7枚見て「ロボ」を種族に含むモンスターを手札に加える。(この効果は各ターンに1度しか使えない)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・「RG」を名称に含むモンスターのレベルを上げる。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・自分のモンスターを1体選ぶ。そのモンスターは次の自分のターンまで、受けるダメージを-2する。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・墓地からatk4以下のモンスターを出す</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・カードを2枚引く。(この効果は各ターンに1度しか使えない)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・相手のすべてのモンスターに2ダメージを与える</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -995,7 +995,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>30</v>
@@ -1010,28 +1010,28 @@
         <v>0</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>45</v>
@@ -1043,13 +1043,13 @@
         <v>43</v>
       </c>
       <c r="R1" s="14" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.4">
@@ -1075,7 +1075,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="H2" s="3">
         <f>_xlfn.XLOOKUP(G2,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
@@ -1089,14 +1089,14 @@
         <v>1</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L2" s="3">
         <f>_xlfn.XLOOKUP(K2,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N2" s="3">
         <f>_xlfn.XLOOKUP(M2,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1115,7 +1115,7 @@
         <v>11</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="S2" s="3">
         <f>_xlfn.XLOOKUP(R2,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1123,8 +1123,8 @@
       </c>
       <c r="T2" s="3" t="str">
         <f>_xlfn.XLOOKUP(A2,Ability!A:A,Ability!B:B,"")</f>
-        <v>①召喚時、手札を1枚捨ててもよい。そうしたら山札の上から5枚見て、種族に「ロボ」を含むカードを１枚手札に加える。
-②レベルアップ</v>
+        <v>・召喚時、手札を1枚捨ててもよい。そうしたら山札の上から5枚見て、種族に「ロボ」を含むカードを１枚手札に加える。
+・レベルアップ</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.4">
@@ -1150,7 +1150,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="H3" s="3">
         <f>_xlfn.XLOOKUP(G3,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
@@ -1164,14 +1164,14 @@
         <v>1</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L3" s="3">
         <f>_xlfn.XLOOKUP(K3,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N3" s="3">
         <f>_xlfn.XLOOKUP(M3,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1190,7 +1190,7 @@
         <v>14</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="S3" s="3">
         <f>_xlfn.XLOOKUP(R3,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1198,9 +1198,9 @@
       </c>
       <c r="T3" s="3" t="str">
         <f>_xlfn.XLOOKUP(A3,Ability!A:A,Ability!B:B,"")</f>
-        <v>①ターン終了時プレイヤーのHPを2回復する。
-②このモンスターが攻撃を受けた時このモンスターのHPを1回復する。
-③レベルアップ</v>
+        <v>・ターン終了時プレイヤーのHPを2回復する。
+・このモンスターが攻撃を受けた時このモンスターのHPを1回復する。
+・レベルアップ</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.4">
@@ -1226,7 +1226,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="H4" s="3">
         <f>_xlfn.XLOOKUP(G4,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
@@ -1240,14 +1240,14 @@
         <v>1</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L4" s="3">
         <f>_xlfn.XLOOKUP(K4,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N4" s="3">
         <f>_xlfn.XLOOKUP(M4,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1266,7 +1266,7 @@
         <v>17</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="S4" s="3">
         <f>_xlfn.XLOOKUP(R4,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1274,10 +1274,10 @@
       </c>
       <c r="T4" s="3" t="str">
         <f>_xlfn.XLOOKUP(A4,Ability!A:A,Ability!B:B,"")</f>
-        <v>①このモンスターが攻撃を受けた時このモンスターのatkを1上昇する。
-②このモンスターの対応役成立時、自分フィールドのモンスター全てと自分のHPを1回復する。
-③このモンスターは効果で破壊されない
-④アスリート</v>
+        <v>・このモンスターが攻撃を受けた時このモンスターのatkを1上昇する。
+・このモンスターの対応役成立時、自分フィールドのモンスター全てと自分のHPを1回復する。
+・このモンスターは効果で破壊されない
+・アスリート</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.4">
@@ -1303,7 +1303,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="H5" s="3">
         <f>_xlfn.XLOOKUP(G5,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
@@ -1317,14 +1317,14 @@
         <v>1</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L5" s="3">
         <f>_xlfn.XLOOKUP(K5,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N5" s="3">
         <f>_xlfn.XLOOKUP(M5,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1343,7 +1343,7 @@
         <v>10</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="S5" s="3">
         <f>_xlfn.XLOOKUP(R5,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1351,10 +1351,10 @@
       </c>
       <c r="T5" s="3" t="str">
         <f>_xlfn.XLOOKUP(A5,Ability!A:A,Ability!B:B,"")</f>
-        <v>①召喚時、相手プレイヤーか相手モンスター1体に2ダメージ。
-②ターン終了時、山札の上から3枚を見てスペルを1枚手札に加える。
-③アスリート
-④レベルアップ</v>
+        <v>・召喚時、相手プレイヤーか相手モンスター1体に2ダメージ。
+・ターン終了時、山札の上から3枚を見てスペルを1枚手札に加える。
+・アスリート
+・レベルアップ</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.4">
@@ -1380,7 +1380,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="H6" s="3">
         <f>_xlfn.XLOOKUP(G6,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
@@ -1394,14 +1394,14 @@
         <v>1</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L6" s="3">
         <f>_xlfn.XLOOKUP(K6,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N6" s="3">
         <f>_xlfn.XLOOKUP(M6,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1420,7 +1420,7 @@
         <v>12</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="S6" s="3">
         <f>_xlfn.XLOOKUP(R6,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1428,10 +1428,10 @@
       </c>
       <c r="T6" s="3" t="str">
         <f>_xlfn.XLOOKUP(A6,Ability!A:A,Ability!B:B,"")</f>
-        <v>①ターン開始時、相手のすべてのモンスターに1ダメージ与える。
-②ターン終了時、相手のランダムなモンスターに3ダメージ与える。
-③アスリート
-④レベルアップ</v>
+        <v>・ターン開始時、相手のすべてのモンスターに1ダメージ与える。
+・ターン終了時、相手のランダムなモンスターに3ダメージ与える。
+・アスリート
+・レベルアップ</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.4">
@@ -1457,7 +1457,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="H7" s="3">
         <f>_xlfn.XLOOKUP(G7,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
@@ -1471,14 +1471,14 @@
         <v>1</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L7" s="3">
         <f>_xlfn.XLOOKUP(K7,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N7" s="3">
         <f>_xlfn.XLOOKUP(M7,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1497,7 +1497,7 @@
         <v>15</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="S7" s="3">
         <f>_xlfn.XLOOKUP(R7,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1505,10 +1505,10 @@
       </c>
       <c r="T7" s="3" t="str">
         <f>_xlfn.XLOOKUP(A7,Ability!A:A,Ability!B:B,"")</f>
-        <v>①ターン開始時、自分のモンスターを1体選ぶ。このターンそのモンスターのatkを+3する。
-②対応役成立時、カードを1枚引く。
-③このモンスターは効果で破壊されない。
-④アスリート</v>
+        <v>・ターン開始時、自分のモンスターを1体選ぶ。このターンそのモンスターのatkを+3する。
+・対応役成立時、カードを1枚引く。
+・このモンスターは効果で破壊されない。
+・アスリート</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.4">
@@ -1534,7 +1534,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="H8" s="3">
         <f>_xlfn.XLOOKUP(G8,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
@@ -1548,14 +1548,14 @@
         <v>1</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L8" s="3">
         <f>_xlfn.XLOOKUP(K8,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N8" s="3">
         <f>_xlfn.XLOOKUP(M8,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1574,7 +1574,7 @@
         <v>4</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="S8" s="3">
         <f>_xlfn.XLOOKUP(R8,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="T8" s="3" t="str">
         <f>_xlfn.XLOOKUP(A8,Ability!A:A,Ability!B:B,"")</f>
-        <v>①ターゲット集中</v>
+        <v>・ターゲット集中</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.4">
@@ -1608,7 +1608,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="H9" s="3">
         <f>_xlfn.XLOOKUP(G9,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
@@ -1622,14 +1622,14 @@
         <v>1</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L9" s="3">
         <f>_xlfn.XLOOKUP(K9,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N9" s="3">
         <f>_xlfn.XLOOKUP(M9,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1648,7 +1648,7 @@
         <v>10</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="S9" s="3">
         <f>_xlfn.XLOOKUP(R9,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1656,8 +1656,8 @@
       </c>
       <c r="T9" s="3" t="str">
         <f>_xlfn.XLOOKUP(A9,Ability!A:A,Ability!B:B,"")</f>
-        <v>①召喚時ランダムな敵に2ダメージ
-②アスリート</v>
+        <v>・召喚時ランダムな敵に2ダメージ
+・アスリート</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.4">
@@ -1683,7 +1683,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="H10" s="3">
         <f>_xlfn.XLOOKUP(G10,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
@@ -1697,14 +1697,14 @@
         <v>1</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L10" s="3">
         <f>_xlfn.XLOOKUP(K10,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N10" s="3">
         <f>_xlfn.XLOOKUP(M10,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1723,7 +1723,7 @@
         <v>10</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="S10" s="3">
         <f>_xlfn.XLOOKUP(R10,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="T10" s="3" t="str">
         <f>_xlfn.XLOOKUP(A10,Ability!A:A,Ability!B:B,"")</f>
-        <v>①ターン終了時、カードを1枚引く。</v>
+        <v>・ターン終了時、カードを1枚引く。</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.4">
@@ -1757,7 +1757,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="H11" s="3">
         <f>_xlfn.XLOOKUP(G11,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
@@ -1771,14 +1771,14 @@
         <v>1</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="L11" s="3">
         <f>_xlfn.XLOOKUP(K11,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>3</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N11" s="3">
         <f>_xlfn.XLOOKUP(M11,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1797,7 +1797,7 @@
         <v>8</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="S11" s="3">
         <f>_xlfn.XLOOKUP(R11,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="T11" s="3" t="str">
         <f>_xlfn.XLOOKUP(A11,Ability!A:A,Ability!B:B,"")</f>
-        <v>①召喚時デッキの上から3枚を見て、その中から「ロボ」モンスターを全て手札に加える。(この効果は各ターン1度しか発動しない。)</v>
+        <v>・召喚時デッキの上から3枚を見て、その中から「ロボ」モンスターを全て手札に加える。(この効果は各ターン1度しか発動しない。)</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.4">
@@ -1831,7 +1831,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="H12" s="3">
         <f>_xlfn.XLOOKUP(G12,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
@@ -1845,14 +1845,14 @@
         <v>1</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L12" s="3">
         <f>_xlfn.XLOOKUP(K12,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N12" s="3">
         <f>_xlfn.XLOOKUP(M12,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1871,7 +1871,7 @@
         <v>30</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="S12" s="3">
         <f>_xlfn.XLOOKUP(R12,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1879,10 +1879,10 @@
       </c>
       <c r="T12" s="3" t="str">
         <f>_xlfn.XLOOKUP(A12,Ability!A:A,Ability!B:B,"")</f>
-        <v>①召喚時、自分のモンスターのHPを全回復する。
-②対応役成立時、このターンこのモンスターのatkを+5する。
-③このモンスターは効果で破壊されない
-④アスリート</v>
+        <v>・召喚時、自分のモンスターのHPを全回復する。
+・対応役成立時、このターンこのモンスターのatkを+5する。
+・このモンスターは効果で破壊されない
+・アスリート</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.4">
@@ -1908,7 +1908,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="H13" s="3">
         <f>_xlfn.XLOOKUP(G13,Koyaku!B$2:B$9,Koyaku!A$2:A$9,"",FALSE)</f>
@@ -1922,14 +1922,14 @@
         <v>1</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L13" s="3">
         <f>_xlfn.XLOOKUP(K13,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>2</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N13" s="3">
         <f>_xlfn.XLOOKUP(M13,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="S13" s="3">
         <f>_xlfn.XLOOKUP(R13,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -1956,10 +1956,10 @@
       </c>
       <c r="T13" s="3" t="str">
         <f>_xlfn.XLOOKUP(A13,Ability!A:A,Ability!B:B,"")</f>
-        <v>①相手のターン中このモンスターのatkは∞になる。
-②このモンスターは離れない。
-③アスリート
-④反撃</v>
+        <v>・相手のターン中このモンスターのatkは∞になる。
+・このモンスターは離れない。
+・アスリート
+・反撃</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.4">
@@ -1999,14 +1999,14 @@
         <v>1</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L14" s="3">
         <f>_xlfn.XLOOKUP(K14,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N14" s="3">
         <f>_xlfn.XLOOKUP(M14,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -2025,7 +2025,7 @@
         <v>-1</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="S14" s="3">
         <f>_xlfn.XLOOKUP(R14,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2033,8 +2033,8 @@
       </c>
       <c r="T14" s="3" t="str">
         <f>_xlfn.XLOOKUP(A14,Ability!A:A,Ability!B:B,"")</f>
-        <v>このターンテーブルを1上昇。(この効果は各ターンに1度しか使えない)
-レベルアップ効果を持つ「RG」モンスターをレベルアップ。</v>
+        <v>・このターンテーブルを1上昇。(この効果は各ターンに1度しか使えない)
+・レベルアップ効果を持つ「RG」モンスターをレベルアップ。</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.4">
@@ -2074,14 +2074,14 @@
         <v>1</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L15" s="3">
         <f>_xlfn.XLOOKUP(K15,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N15" s="3">
         <f>_xlfn.XLOOKUP(M15,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -2100,7 +2100,7 @@
         <v>-1</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="S15" s="3">
         <f>_xlfn.XLOOKUP(R15,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2108,8 +2108,8 @@
       </c>
       <c r="T15" s="3" t="str">
         <f>_xlfn.XLOOKUP(A15,Ability!A:A,Ability!B:B,"")</f>
-        <v>相手のモンスターを1体選ぶ。そのモンスターは次の相手のターンに攻撃できない。
-レベルアップ効果を持つ「RG」１体のモンスターをレベルアップ。</v>
+        <v>・相手のモンスターを1体選ぶ。そのモンスターは次の相手のターンに攻撃できない。
+・レベルアップ効果を持つ「RG」１体のモンスターをレベルアップ。</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.4">
@@ -2149,14 +2149,14 @@
         <v>1</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L16" s="3">
         <f>_xlfn.XLOOKUP(K16,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N16" s="3">
         <f>_xlfn.XLOOKUP(M16,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -2175,7 +2175,7 @@
         <v>-1</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="S16" s="3">
         <f>_xlfn.XLOOKUP(R16,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="T16" s="3" t="str">
         <f>_xlfn.XLOOKUP(A16,Ability!A:A,Ability!B:B,"")</f>
-        <v>次の自分のターンまでモンスター1体に「ターゲット集中」を与える。</v>
+        <v>・次の自分のターンまでモンスター1体に「ターゲット集中」を与える。</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.4">
@@ -2223,14 +2223,14 @@
         <v>1</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L17" s="3">
         <f>_xlfn.XLOOKUP(K17,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N17" s="3">
         <f>_xlfn.XLOOKUP(M17,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -2249,7 +2249,7 @@
         <v>-1</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="S17" s="3">
         <f>_xlfn.XLOOKUP(R17,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="T17" s="3" t="str">
         <f>_xlfn.XLOOKUP(A17,Ability!A:A,Ability!B:B,"")</f>
-        <v>自分のサイズ2以下のモンスターを1体選ぶ。次の自分のターンまでそのモンスターは対応役成立につき2回攻撃する。</v>
+        <v>・自分のサイズ2以下のモンスターを1体選ぶ。次の自分のターンまでそのモンスターは対応役成立につき2回攻撃する。</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.4">
@@ -2297,14 +2297,14 @@
         <v>1</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="L18" s="3">
         <f>_xlfn.XLOOKUP(K18,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>3</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N18" s="3">
         <f>_xlfn.XLOOKUP(M18,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -2323,7 +2323,7 @@
         <v>-1</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="S18" s="3">
         <f>_xlfn.XLOOKUP(R18,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="T18" s="3" t="str">
         <f>_xlfn.XLOOKUP(A18,Ability!A:A,Ability!B:B,"")</f>
-        <v>山札の上から7枚見て「ロボ」を種族に含むモンスターを手札に加える。(この効果は各ターンに1度しか使えない)</v>
+        <v>・山札の上から7枚見て「ロボ」を種族に含むモンスターを手札に加える。(この効果は各ターンに1度しか使えない)</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.4">
@@ -2371,14 +2371,14 @@
         <v>1</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="L19" s="3">
         <f>_xlfn.XLOOKUP(K19,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>3</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N19" s="3">
         <f>_xlfn.XLOOKUP(M19,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -2397,7 +2397,7 @@
         <v>-1</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="S19" s="3">
         <f>_xlfn.XLOOKUP(R19,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="T19" s="3" t="str">
         <f>_xlfn.XLOOKUP(A19,Ability!A:A,Ability!B:B,"")</f>
-        <v>「RG」を名称に含むモンスターのレベルを上げる。</v>
+        <v>・「RG」を名称に含むモンスターのレベルを上げる。</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.4">
@@ -2445,14 +2445,14 @@
         <v>1</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="L20" s="3">
         <f>_xlfn.XLOOKUP(K20,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>3</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N20" s="3">
         <f>_xlfn.XLOOKUP(M20,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -2471,7 +2471,7 @@
         <v>-1</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="S20" s="3">
         <f>_xlfn.XLOOKUP(R20,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="T20" s="3" t="str">
         <f>_xlfn.XLOOKUP(A20,Ability!A:A,Ability!B:B,"")</f>
-        <v>自分のモンスターを1体選ぶ。そのモンスターは次の自分のターンまで、受けるダメージを-2する。</v>
+        <v>・自分のモンスターを1体選ぶ。そのモンスターは次の自分のターンまで、受けるダメージを-2する。</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.4">
@@ -2519,14 +2519,14 @@
         <v>1</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="L21" s="3">
         <f>_xlfn.XLOOKUP(K21,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>3</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N21" s="3">
         <f>_xlfn.XLOOKUP(M21,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -2545,7 +2545,7 @@
         <v>-1</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="S21" s="3">
         <f>_xlfn.XLOOKUP(R21,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="T21" s="3" t="str">
         <f>_xlfn.XLOOKUP(A21,Ability!A:A,Ability!B:B,"")</f>
-        <v>墓地からatk4以下のモンスターを出す</v>
+        <v>・墓地からatk4以下のモンスターを出す</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.4">
@@ -2593,14 +2593,14 @@
         <v>1</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L22" s="3">
         <f>_xlfn.XLOOKUP(K22,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N22" s="3">
         <f>_xlfn.XLOOKUP(M22,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -2619,7 +2619,7 @@
         <v>-1</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="S22" s="3">
         <f>_xlfn.XLOOKUP(R22,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="T22" s="3" t="str">
         <f>_xlfn.XLOOKUP(A22,Ability!A:A,Ability!B:B,"")</f>
-        <v>カードを2枚引く。(この効果は各ターンに1度しか使えない)</v>
+        <v>・カードを2枚引く。(この効果は各ターンに1度しか使えない)</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.4">
@@ -2667,14 +2667,14 @@
         <v>1</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L23" s="3">
         <f>_xlfn.XLOOKUP(K23,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
         <v>-1</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N23" s="3">
         <f>_xlfn.XLOOKUP(M23,Race!B$2:B$5,Race!A$2:A$5,FALSE)</f>
@@ -2693,7 +2693,7 @@
         <v>-1</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="S23" s="3">
         <f>_xlfn.XLOOKUP(R23,Type!$B$2:$B$20,Type!$A$2:$A$20,"")</f>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="T23" s="3" t="str">
         <f>_xlfn.XLOOKUP(A23,Ability!A:A,Ability!B:B,"")</f>
-        <v>相手のすべてのモンスターに2ダメージを与える</v>
+        <v>・相手のすべてのモンスターに2ダメージを与える</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.4">
@@ -2960,7 +2960,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
@@ -2976,7 +2976,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -3151,7 +3151,7 @@
         <v>117</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
@@ -3390,7 +3390,7 @@
         <v>101</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="56.25" x14ac:dyDescent="0.4">
@@ -3399,7 +3399,7 @@
         <v>102</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="75" x14ac:dyDescent="0.4">
@@ -3408,7 +3408,7 @@
         <v>103</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.4">
@@ -3417,7 +3417,7 @@
         <v>104</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.4">
@@ -3426,7 +3426,7 @@
         <v>105</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="75" x14ac:dyDescent="0.4">
@@ -3435,7 +3435,7 @@
         <v>106</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
@@ -3444,7 +3444,7 @@
         <v>107</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="37.5" x14ac:dyDescent="0.4">
@@ -3453,7 +3453,7 @@
         <v>108</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
@@ -3462,7 +3462,7 @@
         <v>109</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
@@ -3471,7 +3471,7 @@
         <v>110</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="75" x14ac:dyDescent="0.4">
@@ -3480,7 +3480,7 @@
         <v>111</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="75" x14ac:dyDescent="0.4">
@@ -3489,7 +3489,7 @@
         <v>112</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="37.5" x14ac:dyDescent="0.4">
@@ -3498,7 +3498,7 @@
         <v>113</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="37.5" x14ac:dyDescent="0.4">
@@ -3507,7 +3507,7 @@
         <v>114</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
@@ -3516,7 +3516,7 @@
         <v>115</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
@@ -3525,7 +3525,7 @@
         <v>116</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
@@ -3534,7 +3534,7 @@
         <v>117</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
@@ -3543,7 +3543,7 @@
         <v>118</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
@@ -3552,7 +3552,7 @@
         <v>119</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
@@ -3561,7 +3561,7 @@
         <v>120</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
@@ -3570,7 +3570,7 @@
         <v>121</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
@@ -3579,12 +3579,13 @@
         <v>122</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3954,7 +3955,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
@@ -3962,7 +3963,7 @@
         <v>-1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
@@ -3978,7 +3979,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
@@ -3986,7 +3987,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -4009,7 +4010,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
@@ -4025,7 +4026,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
@@ -4033,7 +4034,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
@@ -4041,7 +4042,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
@@ -4049,7 +4050,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
@@ -4057,7 +4058,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
@@ -4065,7 +4066,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
@@ -4073,7 +4074,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
